--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4259324</v>
+        <v>4.42153</v>
       </c>
       <c r="G3" t="n">
-        <v>30981</v>
+        <v>30990</v>
       </c>
       <c r="H3" t="n">
-        <v>9200</v>
+        <v>9203</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3915</v>
+        <v>3953</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
         <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25840</v>
+        <v>25811</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6107514</v>
+        <v>3.6090615</v>
       </c>
       <c r="G4" t="n">
-        <v>25101</v>
+        <v>25102</v>
       </c>
       <c r="H4" t="n">
         <v>5608</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7299</v>
+        <v>7310</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -736,10 +736,10 @@
         <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="R4" t="n">
-        <v>14761</v>
+        <v>14751</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.532604</v>
+        <v>4.5311847</v>
       </c>
       <c r="G5" t="n">
-        <v>26655</v>
+        <v>26668</v>
       </c>
       <c r="H5" t="n">
-        <v>9932</v>
+        <v>9936</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>859</v>
       </c>
       <c r="Q5" t="n">
-        <v>1794</v>
+        <v>1807</v>
       </c>
       <c r="R5" t="n">
-        <v>21697</v>
+        <v>21677</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:40</t>
+          <t>2026-09-07 20:13:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3348417</v>
+        <v>4.3378377</v>
       </c>
       <c r="G7" t="n">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="H7" t="n">
         <v>1160</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
         <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>2472</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1657457</v>
+        <v>4.1599264</v>
       </c>
       <c r="G8" t="n">
-        <v>6099</v>
+        <v>6100</v>
       </c>
       <c r="H8" t="n">
         <v>2260</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>999</v>
+        <v>1008</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R8" t="n">
-        <v>4503</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7410715</v>
+        <v>3.7767856</v>
       </c>
       <c r="G9" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H9" t="n">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 6, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9223301</v>
+        <v>3.9326923</v>
       </c>
       <c r="G10" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H10" t="n">
         <v>242</v>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,7 +1290,7 @@
         <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
-        <v>4724</v>
+        <v>4725</v>
       </c>
       <c r="H12" t="n">
         <v>1958</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:41</t>
+          <t>2026-09-07 20:13:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6211524</v>
+        <v>4.6200943</v>
       </c>
       <c r="G14" t="n">
-        <v>13539</v>
+        <v>13546</v>
       </c>
       <c r="H14" t="n">
-        <v>5040</v>
+        <v>5043</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="O14" t="n">
         <v>116</v>
@@ -1472,10 +1472,10 @@
         <v>84</v>
       </c>
       <c r="Q14" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R14" t="n">
-        <v>12031</v>
+        <v>12035</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:42</t>
+          <t>2026-09-07 20:13:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3948126</v>
+        <v>3.4063401</v>
       </c>
       <c r="G15" t="n">
         <v>3926</v>
@@ -1533,11 +1533,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1391</v>
+        <v>1379</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2172</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-06 18:41:42</t>
+          <t>2026-09-07 20:13:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.691142</v>
+        <v>4.691887</v>
       </c>
       <c r="G16" t="n">
         <v>46749</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2364</v>
+        <v>2346</v>
       </c>
       <c r="O16" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="P16" t="n">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="Q16" t="n">
-        <v>2331</v>
+        <v>2335</v>
       </c>
       <c r="R16" t="n">
-        <v>40918</v>
+        <v>40919</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:02</t>
+          <t>2026-09-08 19:38:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:02</t>
+          <t>2026-09-08 19:38:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.42153</v>
+        <v>4.4211097</v>
       </c>
       <c r="G3" t="n">
-        <v>30990</v>
+        <v>31000</v>
       </c>
       <c r="H3" t="n">
-        <v>9203</v>
+        <v>9210</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2418447</v>
+        <v>2420522</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3953</v>
+        <v>3957</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25811</v>
+        <v>25816</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:02</t>
+          <t>2026-09-08 19:38:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6090615</v>
+        <v>3.6037614</v>
       </c>
       <c r="G4" t="n">
-        <v>25102</v>
+        <v>25107</v>
       </c>
       <c r="H4" t="n">
-        <v>5608</v>
+        <v>5609</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2623981</v>
+        <v>2624885</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.1.3</t>
+          <t>2.22.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 2, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7310</v>
+        <v>7342</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="Q4" t="n">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="R4" t="n">
-        <v>14751</v>
+        <v>14717</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:02</t>
+          <t>2026-09-08 19:38:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5311847</v>
+        <v>4.531736</v>
       </c>
       <c r="G5" t="n">
-        <v>26668</v>
+        <v>26676</v>
       </c>
       <c r="H5" t="n">
-        <v>9936</v>
+        <v>9941</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="O5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="Q5" t="n">
-        <v>1807</v>
+        <v>1792</v>
       </c>
       <c r="R5" t="n">
-        <v>21677</v>
+        <v>21696</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:03</t>
+          <t>2026-09-08 19:38:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:03</t>
+          <t>2026-09-08 19:38:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:03</t>
+          <t>2026-09-08 19:38:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1599264</v>
+        <v>4.161468</v>
       </c>
       <c r="G8" t="n">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="H8" t="n">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>257</v>
       </c>
       <c r="R8" t="n">
-        <v>4495</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:03</t>
+          <t>2026-09-08 19:38:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1277</v>
       </c>
       <c r="H9" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:04</t>
+          <t>2026-09-08 19:38:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:04</t>
+          <t>2026-09-08 19:39:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6781697</v>
+        <v>4.678411</v>
       </c>
       <c r="G11" t="n">
-        <v>15002</v>
+        <v>15003</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1257,7 +1257,7 @@
         <v>843</v>
       </c>
       <c r="R11" t="n">
-        <v>12998</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:04</t>
+          <t>2026-09-08 19:39:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>358227</v>
+        <v>358322</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:04</t>
+          <t>2026-09-08 19:39:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:04</t>
+          <t>2026-09-08 19:39:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6200943</v>
+        <v>4.619531</v>
       </c>
       <c r="G14" t="n">
-        <v>13546</v>
+        <v>13551</v>
       </c>
       <c r="H14" t="n">
-        <v>5043</v>
+        <v>5045</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="O14" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="P14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q14" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R14" t="n">
-        <v>12035</v>
+        <v>12037</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:05</t>
+          <t>2026-09-08 19:39:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         <v>3926</v>
       </c>
       <c r="H15" t="n">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>409397</v>
+        <v>410228</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 20:13:05</t>
+          <t>2026-09-08 19:39:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.691887</v>
+        <v>4.6921463</v>
       </c>
       <c r="G16" t="n">
-        <v>46749</v>
+        <v>46748</v>
       </c>
       <c r="H16" t="n">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>587217</v>
+        <v>587781</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2346</v>
+        <v>2353</v>
       </c>
       <c r="O16" t="n">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="P16" t="n">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="Q16" t="n">
-        <v>2335</v>
+        <v>2330</v>
       </c>
       <c r="R16" t="n">
-        <v>40919</v>
+        <v>40929</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:57</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40603</v>
+        <v>40672</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:58</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4211097</v>
+        <v>4.4192615</v>
       </c>
       <c r="G3" t="n">
-        <v>31000</v>
+        <v>31012</v>
       </c>
       <c r="H3" t="n">
-        <v>9210</v>
+        <v>9213</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3957</v>
+        <v>3973</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25816</v>
+        <v>25812</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:58</t>
+          <t>2026-09-09 19:33:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6037614</v>
+        <v>3.6029792</v>
       </c>
       <c r="G4" t="n">
-        <v>25107</v>
+        <v>25111</v>
       </c>
       <c r="H4" t="n">
         <v>5609</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7342</v>
+        <v>7351</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="R4" t="n">
-        <v>14717</v>
+        <v>14718</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:58</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.531736</v>
+        <v>4.532773</v>
       </c>
       <c r="G5" t="n">
-        <v>26676</v>
+        <v>26692</v>
       </c>
       <c r="H5" t="n">
-        <v>9941</v>
+        <v>9948</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>677238</v>
+        <v>677644</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="O5" t="n">
         <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="Q5" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="R5" t="n">
-        <v>21696</v>
+        <v>21711</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:58</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112034</v>
+        <v>112224</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:59</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3378377</v>
+        <v>4.340807</v>
       </c>
       <c r="G7" t="n">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="H7" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>456331</v>
+        <v>456879</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O7" t="n">
         <v>55</v>
@@ -958,10 +958,10 @@
         <v>112</v>
       </c>
       <c r="Q7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2476</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:59</t>
+          <t>2026-09-09 19:33:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.161468</v>
+        <v>4.1630034</v>
       </c>
       <c r="G8" t="n">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>458765</v>
+        <v>459258</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1032,10 +1032,10 @@
         <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="R8" t="n">
-        <v>4499</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:59</t>
+          <t>2026-09-09 19:33:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,10 +1068,10 @@
         <v>3.7767856</v>
       </c>
       <c r="G9" t="n">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="H9" t="n">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>182238</v>
+        <v>182393</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08 19:38:59</t>
+          <t>2026-09-09 19:33:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:00</t>
+          <t>2026-09-09 19:33:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.678411</v>
+        <v>4.678892</v>
       </c>
       <c r="G11" t="n">
-        <v>15003</v>
+        <v>15006</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274873</v>
+        <v>275014</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="O11" t="n">
         <v>111</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q11" t="n">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="R11" t="n">
-        <v>13000</v>
+        <v>13005</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:00</t>
+          <t>2026-09-09 19:33:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>4725</v>
       </c>
       <c r="H12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>358322</v>
+        <v>358554</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:00</t>
+          <t>2026-09-09 19:33:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22278</v>
+        <v>22285</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:00</t>
+          <t>2026-09-09 19:33:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.619531</v>
+        <v>4.612981</v>
       </c>
       <c r="G14" t="n">
-        <v>13551</v>
+        <v>13571</v>
       </c>
       <c r="H14" t="n">
-        <v>5045</v>
+        <v>5047</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1280610</v>
+        <v>1283435</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="O14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="P14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q14" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="R14" t="n">
-        <v>12037</v>
+        <v>12026</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:01</t>
+          <t>2026-09-09 19:33:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4063401</v>
+        <v>3.4178674</v>
       </c>
       <c r="G15" t="n">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="H15" t="n">
         <v>1588</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>410228</v>
+        <v>410560</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1379</v>
+        <v>1368</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2182</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-08 19:39:01</t>
+          <t>2026-09-09 19:33:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6921463</v>
+        <v>4.6929116</v>
       </c>
       <c r="G16" t="n">
-        <v>46748</v>
+        <v>46750</v>
       </c>
       <c r="H16" t="n">
         <v>2994</v>
@@ -1593,11 +1593,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>587781</v>
+        <v>588790</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.6</t>
+          <t>3.1.7</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1607,23 +1607,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Sep 9, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2353</v>
+        <v>2335</v>
       </c>
       <c r="O16" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="P16" t="n">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="Q16" t="n">
-        <v>2330</v>
+        <v>2335</v>
       </c>
       <c r="R16" t="n">
-        <v>40929</v>
+        <v>40934</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-10 19:19:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40672</v>
+        <v>40786</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-10 19:19:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4192615</v>
+        <v>4.4173913</v>
       </c>
       <c r="G3" t="n">
-        <v>31012</v>
+        <v>31018</v>
       </c>
       <c r="H3" t="n">
-        <v>9213</v>
+        <v>9215</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2420522</v>
+        <v>2424584</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3973</v>
+        <v>3989</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25812</v>
+        <v>25802</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:21</t>
+          <t>2026-09-10 19:19:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6029792</v>
       </c>
       <c r="G4" t="n">
-        <v>25111</v>
+        <v>25112</v>
       </c>
       <c r="H4" t="n">
         <v>5609</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2624885</v>
+        <v>2626700</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-10 19:19:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.532773</v>
+        <v>4.530988</v>
       </c>
       <c r="G5" t="n">
-        <v>26692</v>
+        <v>26714</v>
       </c>
       <c r="H5" t="n">
-        <v>9948</v>
+        <v>9950</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>677644</v>
+        <v>678569</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="Q5" t="n">
-        <v>1793</v>
+        <v>1800</v>
       </c>
       <c r="R5" t="n">
-        <v>21711</v>
+        <v>21723</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-10 19:19:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-10 19:19:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.340807</v>
+        <v>4.34375</v>
       </c>
       <c r="G7" t="n">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="H7" t="n">
         <v>1161</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O7" t="n">
         <v>55</v>
@@ -961,7 +961,7 @@
         <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2480</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:22</t>
+          <t>2026-09-10 19:19:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1630034</v>
+        <v>4.1608777</v>
       </c>
       <c r="G8" t="n">
-        <v>6102</v>
+        <v>6103</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>459258</v>
+        <v>460610</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="Q8" t="n">
         <v>255</v>
       </c>
       <c r="R8" t="n">
-        <v>4503</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:23</t>
+          <t>2026-09-10 19:19:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,10 +1068,10 @@
         <v>3.7767856</v>
       </c>
       <c r="G9" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H9" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>182393</v>
+        <v>182747</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:23</t>
+          <t>2026-09-10 19:19:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>568</v>
       </c>
       <c r="H10" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>95043</v>
+        <v>95343</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:23</t>
+          <t>2026-09-10 19:19:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>275014</v>
+        <v>275250</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:23</t>
+          <t>2026-09-10 19:19:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1290,7 +1290,7 @@
         <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
-        <v>4725</v>
+        <v>4726</v>
       </c>
       <c r="H12" t="n">
         <v>1959</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>358554</v>
+        <v>358880</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:24</t>
+          <t>2026-09-10 19:19:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22285</v>
+        <v>22294</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:24</t>
+          <t>2026-09-10 19:19:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.612981</v>
+        <v>4.6145253</v>
       </c>
       <c r="G14" t="n">
-        <v>13571</v>
+        <v>13575</v>
       </c>
       <c r="H14" t="n">
-        <v>5047</v>
+        <v>5049</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="O14" t="n">
         <v>129</v>
       </c>
       <c r="P14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="n">
         <v>205</v>
       </c>
       <c r="R14" t="n">
-        <v>12026</v>
+        <v>12035</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:24</t>
+          <t>2026-09-10 19:19:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.4178674</v>
       </c>
       <c r="G15" t="n">
-        <v>3927</v>
+        <v>3928</v>
       </c>
       <c r="H15" t="n">
         <v>1588</v>
@@ -1533,11 +1533,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:24</t>
+          <t>2026-09-10 19:19:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6929116</v>
+        <v>4.6929846</v>
       </c>
       <c r="G16" t="n">
         <v>46750</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="O16" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P16" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="Q16" t="n">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="R16" t="n">
-        <v>40934</v>
+        <v>40935</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:44</t>
+          <t>2026-09-11 19:20:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:45</t>
+          <t>2026-09-11 19:20:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4173913</v>
+        <v>4.41489</v>
       </c>
       <c r="G3" t="n">
-        <v>31018</v>
+        <v>31025</v>
       </c>
       <c r="H3" t="n">
         <v>9215</v>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Aug 25, 2026</t>
+          <t>Sep 8, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3989</v>
+        <v>4001</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25802</v>
+        <v>25788</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:45</t>
+          <t>2026-09-11 19:20:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6029792</v>
       </c>
       <c r="G4" t="n">
-        <v>25112</v>
+        <v>25114</v>
       </c>
       <c r="H4" t="n">
         <v>5609</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2626700</v>
+        <v>2629150</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1284</v>
       </c>
       <c r="R4" t="n">
-        <v>14718</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:45</t>
+          <t>2026-09-11 19:20:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.530988</v>
+        <v>4.532749</v>
       </c>
       <c r="G5" t="n">
-        <v>26714</v>
+        <v>26721</v>
       </c>
       <c r="H5" t="n">
-        <v>9950</v>
+        <v>9951</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>678569</v>
+        <v>679762</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P5" t="n">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="Q5" t="n">
-        <v>1800</v>
+        <v>1793</v>
       </c>
       <c r="R5" t="n">
-        <v>21723</v>
+        <v>21749</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:45</t>
+          <t>2026-09-11 19:20:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112224</v>
+        <v>112414</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.0.1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 2, 2026</t>
+          <t>Sep 9, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:46</t>
+          <t>2026-09-11 19:20:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>3144</v>
       </c>
       <c r="H7" t="n">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>456879</v>
+        <v>457375</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:46</t>
+          <t>2026-09-11 19:20:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1608777</v>
       </c>
       <c r="G8" t="n">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>460610</v>
+        <v>463005</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:46</t>
+          <t>2026-09-11 19:20:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,7 +1068,7 @@
         <v>3.7767856</v>
       </c>
       <c r="G9" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H9" t="n">
         <v>532</v>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:46</t>
+          <t>2026-09-11 19:20:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9326923</v>
+        <v>3.9047618</v>
       </c>
       <c r="G10" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H10" t="n">
         <v>243</v>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:47</t>
+          <t>2026-09-11 19:20:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>275250</v>
+        <v>275589</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:47</t>
+          <t>2026-09-11 19:20:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:47</t>
+          <t>2026-09-11 19:20:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22294</v>
+        <v>22311</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:47</t>
+          <t>2026-09-11 19:20:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6145253</v>
+        <v>4.6122613</v>
       </c>
       <c r="G14" t="n">
-        <v>13575</v>
+        <v>13578</v>
       </c>
       <c r="H14" t="n">
         <v>5049</v>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1283435</v>
+        <v>1286112</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="O14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P14" t="n">
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R14" t="n">
-        <v>12035</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:48</t>
+          <t>2026-09-11 19:20:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>410560</v>
+        <v>411495</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10 19:19:48</t>
+          <t>2026-09-11 19:20:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6929846</v>
+        <v>4.692015</v>
       </c>
       <c r="G16" t="n">
-        <v>46750</v>
+        <v>46752</v>
       </c>
       <c r="H16" t="n">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="O16" t="n">
         <v>388</v>
@@ -1620,10 +1620,10 @@
         <v>755</v>
       </c>
       <c r="Q16" t="n">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="R16" t="n">
-        <v>40935</v>
+        <v>40918</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:51</t>
+          <t>2026-09-13 19:01:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40786</v>
+        <v>41009</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:51</t>
+          <t>2026-09-13 19:01:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.41489</v>
+        <v>4.4194717</v>
       </c>
       <c r="G3" t="n">
-        <v>31025</v>
+        <v>31039</v>
       </c>
       <c r="H3" t="n">
-        <v>9215</v>
+        <v>9219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4001</v>
+        <v>3975</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25788</v>
+        <v>25837</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:52</t>
+          <t>2026-09-13 19:01:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6029792</v>
+        <v>3.602713</v>
       </c>
       <c r="G4" t="n">
-        <v>25114</v>
+        <v>25119</v>
       </c>
       <c r="H4" t="n">
-        <v>5609</v>
+        <v>5610</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7351</v>
+        <v>7349</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="R4" t="n">
-        <v>14720</v>
+        <v>14717</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:52</t>
+          <t>2026-09-13 19:01:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.532749</v>
+        <v>4.529732</v>
       </c>
       <c r="G5" t="n">
-        <v>26721</v>
+        <v>26729</v>
       </c>
       <c r="H5" t="n">
-        <v>9951</v>
+        <v>9960</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2017</v>
+        <v>2037</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1793</v>
+        <v>1812</v>
       </c>
       <c r="R5" t="n">
-        <v>21749</v>
+        <v>21724</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:52</t>
+          <t>2026-09-13 19:01:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:52</t>
+          <t>2026-09-13 19:01:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.34375</v>
+        <v>4.328889</v>
       </c>
       <c r="G7" t="n">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="H7" t="n">
         <v>1162</v>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="O7" t="n">
         <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
         <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2483</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:53</t>
+          <t>2026-09-13 19:01:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1608777</v>
+        <v>4.158088</v>
       </c>
       <c r="G8" t="n">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q8" t="n">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4495</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:53</t>
+          <t>2026-09-13 19:01:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,7 +1068,7 @@
         <v>3.7767856</v>
       </c>
       <c r="G9" t="n">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="H9" t="n">
         <v>532</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>182747</v>
+        <v>183090</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:53</t>
+          <t>2026-09-13 19:01:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>95343</v>
+        <v>95635</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:53</t>
+          <t>2026-09-13 19:01:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:54</t>
+          <t>2026-09-13 19:01:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7467701</v>
+        <v>2.742268</v>
       </c>
       <c r="G12" t="n">
-        <v>4726</v>
+        <v>4727</v>
       </c>
       <c r="H12" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2405</v>
+        <v>2412</v>
       </c>
       <c r="O12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1769</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:54</t>
+          <t>2026-09-13 19:01:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:54</t>
+          <t>2026-09-13 19:01:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6122613</v>
+        <v>4.610935</v>
       </c>
       <c r="G14" t="n">
-        <v>13578</v>
+        <v>13584</v>
       </c>
       <c r="H14" t="n">
-        <v>5049</v>
+        <v>5052</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="O14" t="n">
         <v>128</v>
@@ -1472,10 +1472,10 @@
         <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R14" t="n">
-        <v>12031</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:54</t>
+          <t>2026-09-13 19:01:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4178674</v>
+        <v>3.4063401</v>
       </c>
       <c r="G15" t="n">
-        <v>3928</v>
+        <v>3930</v>
       </c>
       <c r="H15" t="n">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1533,11 +1533,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Sep 12, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1549,7 +1549,7 @@
         <v>124</v>
       </c>
       <c r="R15" t="n">
-        <v>2195</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-11 19:20:55</t>
+          <t>2026-09-13 19:01:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.692015</v>
+        <v>4.6922345</v>
       </c>
       <c r="G16" t="n">
-        <v>46752</v>
+        <v>46755</v>
       </c>
       <c r="H16" t="n">
-        <v>2995</v>
+        <v>2997</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>588790</v>
+        <v>590411</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="O16" t="n">
         <v>388</v>
       </c>
       <c r="P16" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="Q16" t="n">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="R16" t="n">
-        <v>40918</v>
+        <v>40925</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:47</t>
+          <t>2026-09-14 20:40:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41009</v>
+        <v>41200</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:48</t>
+          <t>2026-09-14 20:40:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4194717</v>
+        <v>4.416365</v>
       </c>
       <c r="G3" t="n">
-        <v>31039</v>
+        <v>31045</v>
       </c>
       <c r="H3" t="n">
-        <v>9219</v>
+        <v>9221</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2424584</v>
+        <v>2427628</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.45.1</t>
+          <t>4.46.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3975</v>
+        <v>4000</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25837</v>
+        <v>25817</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:48</t>
+          <t>2026-09-14 20:40:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.602713</v>
+        <v>3.6001296</v>
       </c>
       <c r="G4" t="n">
-        <v>25119</v>
+        <v>25123</v>
       </c>
       <c r="H4" t="n">
         <v>5610</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7349</v>
+        <v>7374</v>
       </c>
       <c r="O4" t="n">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="Q4" t="n">
-        <v>1280</v>
+        <v>1269</v>
       </c>
       <c r="R4" t="n">
-        <v>14717</v>
+        <v>14718</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:48</t>
+          <t>2026-09-14 20:40:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.529732</v>
+        <v>4.5306206</v>
       </c>
       <c r="G5" t="n">
-        <v>26729</v>
+        <v>26750</v>
       </c>
       <c r="H5" t="n">
-        <v>9960</v>
+        <v>9967</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>679762</v>
+        <v>681241</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="Q5" t="n">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="R5" t="n">
-        <v>21724</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:48</t>
+          <t>2026-09-14 20:40:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:48</t>
+          <t>2026-09-14 20:40:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:49</t>
+          <t>2026-09-14 20:40:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.158088</v>
+        <v>4.159633</v>
       </c>
       <c r="G8" t="n">
-        <v>6104</v>
+        <v>6105</v>
       </c>
       <c r="H8" t="n">
         <v>2261</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4498</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:49</t>
+          <t>2026-09-14 20:40:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7767856</v>
+        <v>3.7876105</v>
       </c>
       <c r="G9" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H9" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:49</t>
+          <t>2026-09-14 20:40:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9047618</v>
+        <v>3.89</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H10" t="n">
         <v>243</v>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:49</t>
+          <t>2026-09-14 20:40:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:49</t>
+          <t>2026-09-14 20:40:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.742268</v>
+        <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
-        <v>4727</v>
+        <v>4726</v>
       </c>
       <c r="H12" t="n">
         <v>1960</v>
@@ -1315,10 +1315,10 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2412</v>
+        <v>2405</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P12" t="n">
         <v>206</v>
@@ -1327,7 +1327,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1766</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:50</t>
+          <t>2026-09-14 20:40:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:50</t>
+          <t>2026-09-14 20:40:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.610935</v>
+        <v>4.605845</v>
       </c>
       <c r="G14" t="n">
-        <v>13584</v>
+        <v>13586</v>
       </c>
       <c r="H14" t="n">
-        <v>5052</v>
+        <v>5054</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,11 +1445,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1286112</v>
+        <v>1288575</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.6.5</t>
+          <t>10.6.7</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1459,11 +1459,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>May 20, 2026</t>
+          <t>Sep 11, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1129</v>
+        <v>1147</v>
       </c>
       <c r="O14" t="n">
         <v>128</v>
@@ -1475,7 +1475,7 @@
         <v>203</v>
       </c>
       <c r="R14" t="n">
-        <v>12033</v>
+        <v>12018</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:50</t>
+          <t>2026-09-14 20:40:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4063401</v>
+        <v>3.408046</v>
       </c>
       <c r="G15" t="n">
-        <v>3930</v>
+        <v>3933</v>
       </c>
       <c r="H15" t="n">
         <v>1589</v>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="O15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="R15" t="n">
-        <v>2185</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-13 19:01:50</t>
+          <t>2026-09-14 20:40:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1582,7 +1582,7 @@
         <v>4.6922345</v>
       </c>
       <c r="G16" t="n">
-        <v>46755</v>
+        <v>46756</v>
       </c>
       <c r="H16" t="n">
         <v>2997</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:19</t>
+          <t>2026-09-15 19:53:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41200</v>
+        <v>41296</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:19</t>
+          <t>2026-09-15 19:53:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.416365</v>
+        <v>4.418655</v>
       </c>
       <c r="G3" t="n">
-        <v>31045</v>
+        <v>31050</v>
       </c>
       <c r="H3" t="n">
-        <v>9221</v>
+        <v>9227</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4000</v>
+        <v>3984</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25817</v>
+        <v>25841</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:19</t>
+          <t>2026-09-15 19:53:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6001296</v>
       </c>
       <c r="G4" t="n">
-        <v>25123</v>
+        <v>25121</v>
       </c>
       <c r="H4" t="n">
-        <v>5610</v>
+        <v>5611</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2629150</v>
+        <v>2631471</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1269</v>
       </c>
       <c r="R4" t="n">
-        <v>14718</v>
+        <v>14716</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:19</t>
+          <t>2026-09-15 19:53:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5306206</v>
+        <v>4.528822</v>
       </c>
       <c r="G5" t="n">
-        <v>26750</v>
+        <v>26761</v>
       </c>
       <c r="H5" t="n">
-        <v>9967</v>
+        <v>9971</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2041</v>
+        <v>2056</v>
       </c>
       <c r="O5" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="Q5" t="n">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="R5" t="n">
-        <v>21755</v>
+        <v>21752</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:20</t>
+          <t>2026-09-15 19:53:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112414</v>
+        <v>112536</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:20</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>457375</v>
+        <v>457825</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:20</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>6105</v>
       </c>
       <c r="H8" t="n">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>463005</v>
+        <v>465039</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:20</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7876105</v>
+        <v>3.7699115</v>
       </c>
       <c r="G9" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H9" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>183090</v>
+        <v>183296</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 6, 2026</t>
+          <t>Sep 7, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
       </c>
       <c r="P9" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:20</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>95635</v>
+        <v>95823</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:21</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>275589</v>
+        <v>275878</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:21</t>
+          <t>2026-09-15 19:53:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>358880</v>
+        <v>359105</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:21</t>
+          <t>2026-09-15 19:54:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22311</v>
+        <v>22332</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:21</t>
+          <t>2026-09-15 19:54:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.605845</v>
+        <v>4.601415</v>
       </c>
       <c r="G14" t="n">
-        <v>13586</v>
+        <v>13593</v>
       </c>
       <c r="H14" t="n">
-        <v>5054</v>
+        <v>5060</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,11 +1445,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1288575</v>
+        <v>1289796</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.6.7</t>
+          <t>10.6.8</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1459,23 +1459,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sep 11, 2026</t>
+          <t>Sep 14, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1147</v>
+        <v>1163</v>
       </c>
       <c r="O14" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q14" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R14" t="n">
-        <v>12018</v>
+        <v>12011</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:21</t>
+          <t>2026-09-15 19:54:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.408046</v>
+        <v>3.4126074</v>
       </c>
       <c r="G15" t="n">
         <v>3933</v>
       </c>
       <c r="H15" t="n">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>411495</v>
+        <v>412498</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="O15" t="n">
         <v>134</v>
@@ -1549,7 +1549,7 @@
         <v>134</v>
       </c>
       <c r="R15" t="n">
-        <v>2180</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 20:40:22</t>
+          <t>2026-09-15 19:54:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6922345</v>
+        <v>4.6921616</v>
       </c>
       <c r="G16" t="n">
-        <v>46756</v>
+        <v>46754</v>
       </c>
       <c r="H16" t="n">
         <v>2997</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>590411</v>
+        <v>593003</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="O16" t="n">
         <v>388</v>
       </c>
       <c r="P16" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="Q16" t="n">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="R16" t="n">
-        <v>40925</v>
+        <v>40922</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:58</t>
+          <t>2026-09-16 19:47:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:58</t>
+          <t>2026-09-16 19:47:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.418655</v>
+        <v>4.416365</v>
       </c>
       <c r="G3" t="n">
-        <v>31050</v>
+        <v>31057</v>
       </c>
       <c r="H3" t="n">
-        <v>9227</v>
+        <v>9229</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2427628</v>
+        <v>2429952</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Sep 8, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3984</v>
+        <v>4001</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25841</v>
+        <v>25828</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:58</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6001296</v>
+        <v>3.6010363</v>
       </c>
       <c r="G4" t="n">
-        <v>25121</v>
+        <v>25125</v>
       </c>
       <c r="H4" t="n">
         <v>5611</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7374</v>
+        <v>7370</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14716</v>
+        <v>14726</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:58</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.528822</v>
+        <v>4.5324674</v>
       </c>
       <c r="G5" t="n">
-        <v>26761</v>
+        <v>26773</v>
       </c>
       <c r="H5" t="n">
         <v>9971</v>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>681241</v>
+        <v>682142</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Sep 14, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2056</v>
+        <v>2029</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="R5" t="n">
-        <v>21752</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:58</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.159633</v>
+        <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="H8" t="n">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>4502</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7699115</v>
+        <v>3.716814</v>
       </c>
       <c r="G9" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="H9" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>831</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>570</v>
       </c>
       <c r="H10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:53:59</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:00</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:00</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.601415</v>
+        <v>4.6009283</v>
       </c>
       <c r="G14" t="n">
-        <v>13593</v>
+        <v>13614</v>
       </c>
       <c r="H14" t="n">
-        <v>5060</v>
+        <v>5065</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1289796</v>
+        <v>1290305</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="O14" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="P14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q14" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="R14" t="n">
-        <v>12011</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:00</t>
+          <t>2026-09-16 19:47:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4126074</v>
+        <v>3.4149857</v>
       </c>
       <c r="G15" t="n">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="H15" t="n">
         <v>1590</v>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="O15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R15" t="n">
-        <v>2185</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:54:00</t>
+          <t>2026-09-16 19:47:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
         <v>46754</v>
       </c>
       <c r="H16" t="n">
-        <v>2997</v>
+        <v>2999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>2343</v>
       </c>
       <c r="R16" t="n">
-        <v>40922</v>
+        <v>40923</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:18</t>
+          <t>2026-09-17 19:56:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2" t="n">
         <v>179</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:18</t>
+          <t>2026-09-17 19:56:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.416365</v>
+        <v>4.412658</v>
       </c>
       <c r="G3" t="n">
-        <v>31057</v>
+        <v>31061</v>
       </c>
       <c r="H3" t="n">
-        <v>9229</v>
+        <v>9231</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4001</v>
+        <v>4032</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25828</v>
+        <v>25802</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.6010363</v>
       </c>
       <c r="G4" t="n">
-        <v>25125</v>
+        <v>25124</v>
       </c>
       <c r="H4" t="n">
         <v>5611</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2631471</v>
+        <v>2633254</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14726</v>
+        <v>14725</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5324674</v>
+        <v>4.5307918</v>
       </c>
       <c r="G5" t="n">
-        <v>26773</v>
+        <v>26774</v>
       </c>
       <c r="H5" t="n">
-        <v>9971</v>
+        <v>9974</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2029</v>
+        <v>2040</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
@@ -813,7 +813,7 @@
         <v>1827</v>
       </c>
       <c r="R5" t="n">
-        <v>21780</v>
+        <v>21770</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112536</v>
+        <v>112615</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>457825</v>
+        <v>458165</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1691175</v>
+        <v>4.1706424</v>
       </c>
       <c r="G8" t="n">
-        <v>6108</v>
+        <v>6109</v>
       </c>
       <c r="H8" t="n">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>465039</v>
+        <v>466867</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4524</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:19</t>
+          <t>2026-09-17 19:56:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.716814</v>
+        <v>3.6578948</v>
       </c>
       <c r="G9" t="n">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="H9" t="n">
         <v>538</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>183296</v>
+        <v>183566</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="O9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>820</v>
+        <v>803</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.89</v>
+        <v>3.8333333</v>
       </c>
       <c r="G10" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>95823</v>
+        <v>96120</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.678892</v>
+        <v>4.6817155</v>
       </c>
       <c r="G11" t="n">
         <v>15006</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>275878</v>
+        <v>276075</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="O11" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="R11" t="n">
-        <v>13005</v>
+        <v>13029</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>359105</v>
+        <v>359442</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22332</v>
+        <v>22345</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6009283</v>
+        <v>4.582866</v>
       </c>
       <c r="G14" t="n">
-        <v>13614</v>
+        <v>13649</v>
       </c>
       <c r="H14" t="n">
-        <v>5065</v>
+        <v>5074</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1157</v>
+        <v>1201</v>
       </c>
       <c r="O14" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="P14" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="R14" t="n">
-        <v>12013</v>
+        <v>11954</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:20</t>
+          <t>2026-09-17 19:56:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1508,7 +1508,7 @@
         <v>3.4149857</v>
       </c>
       <c r="G15" t="n">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="H15" t="n">
         <v>1590</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>412498</v>
+        <v>413364</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1549,7 +1549,7 @@
         <v>135</v>
       </c>
       <c r="R15" t="n">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-16 19:47:21</t>
+          <t>2026-09-17 19:56:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6921616</v>
+        <v>4.691997</v>
       </c>
       <c r="G16" t="n">
-        <v>46754</v>
+        <v>46753</v>
       </c>
       <c r="H16" t="n">
         <v>2999</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O16" t="n">
         <v>388</v>
       </c>
       <c r="P16" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="Q16" t="n">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="R16" t="n">
-        <v>40923</v>
+        <v>40912</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:15</t>
+          <t>2026-09-18 19:16:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:15</t>
+          <t>2026-09-18 19:16:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.412658</v>
+        <v>4.4109983</v>
       </c>
       <c r="G3" t="n">
-        <v>31061</v>
+        <v>31067</v>
       </c>
       <c r="H3" t="n">
-        <v>9231</v>
+        <v>9235</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.0</t>
+          <t>4.46.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4032</v>
+        <v>4045</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25802</v>
+        <v>25794</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:16</t>
+          <t>2026-09-18 19:16:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.6010363</v>
       </c>
       <c r="G4" t="n">
-        <v>25124</v>
+        <v>25127</v>
       </c>
       <c r="H4" t="n">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7370</v>
+        <v>7371</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -739,7 +739,7 @@
         <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14725</v>
+        <v>14727</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:16</t>
+          <t>2026-09-18 19:16:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5307918</v>
+        <v>4.5286493</v>
       </c>
       <c r="G5" t="n">
-        <v>26774</v>
+        <v>26780</v>
       </c>
       <c r="H5" t="n">
-        <v>9974</v>
+        <v>9976</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2040</v>
+        <v>2049</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="Q5" t="n">
-        <v>1827</v>
+        <v>1836</v>
       </c>
       <c r="R5" t="n">
-        <v>21770</v>
+        <v>21749</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:17</t>
+          <t>2026-09-18 19:16:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:17</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.328889</v>
+        <v>4.3318586</v>
       </c>
       <c r="G7" t="n">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="H7" t="n">
         <v>1162</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="O7" t="n">
         <v>55</v>
@@ -961,7 +961,7 @@
         <v>97</v>
       </c>
       <c r="R7" t="n">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:18</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1706424</v>
+        <v>4.164835</v>
       </c>
       <c r="G8" t="n">
-        <v>6109</v>
+        <v>6110</v>
       </c>
       <c r="H8" t="n">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4528</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:18</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6578948</v>
+        <v>3.6371682</v>
       </c>
       <c r="G9" t="n">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H9" t="n">
         <v>538</v>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 7, 2026</t>
+          <t>Sep 6, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="O9" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:18</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8333333</v>
+        <v>3.8557692</v>
       </c>
       <c r="G10" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H10" t="n">
         <v>246</v>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:19</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>4.6817155</v>
       </c>
       <c r="G11" t="n">
-        <v>15006</v>
+        <v>15007</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1254,10 +1254,10 @@
         <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="R11" t="n">
-        <v>13029</v>
+        <v>13030</v>
       </c>
     </row>
     <row r="12">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:19</t>
+          <t>2026-09-18 19:16:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:20</t>
+          <t>2026-09-18 19:16:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:21</t>
+          <t>2026-09-18 19:16:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.582866</v>
+        <v>4.5653906</v>
       </c>
       <c r="G14" t="n">
-        <v>13649</v>
+        <v>13674</v>
       </c>
       <c r="H14" t="n">
-        <v>5074</v>
+        <v>5081</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1201</v>
+        <v>1253</v>
       </c>
       <c r="O14" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="P14" t="n">
         <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="R14" t="n">
-        <v>11954</v>
+        <v>11907</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:21</t>
+          <t>2026-09-18 19:16:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4149857</v>
+        <v>3.4236312</v>
       </c>
       <c r="G15" t="n">
-        <v>3933</v>
+        <v>3937</v>
       </c>
       <c r="H15" t="n">
         <v>1590</v>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1546,10 +1546,10 @@
         <v>101</v>
       </c>
       <c r="Q15" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2186</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="16">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-17 19:56:22</t>
+          <t>2026-09-18 19:16:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
         <v>46753</v>
       </c>
       <c r="H16" t="n">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:24</t>
+          <t>2026-09-19 19:01:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Jul 2, 2026</t>
+          <t>Sep 15, 2026</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:24</t>
+          <t>2026-09-19 19:01:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4109983</v>
+        <v>4.4077425</v>
       </c>
       <c r="G3" t="n">
-        <v>31067</v>
+        <v>31077</v>
       </c>
       <c r="H3" t="n">
-        <v>9235</v>
+        <v>9237</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4045</v>
+        <v>4080</v>
       </c>
       <c r="O3" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
         <v>280</v>
@@ -665,7 +665,7 @@
         <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25794</v>
+        <v>25780</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:24</t>
+          <t>2026-09-19 19:01:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6010363</v>
+        <v>3.6028461</v>
       </c>
       <c r="G4" t="n">
-        <v>25127</v>
+        <v>25129</v>
       </c>
       <c r="H4" t="n">
         <v>5612</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7371</v>
+        <v>7361</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -736,10 +736,10 @@
         <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="R4" t="n">
-        <v>14727</v>
+        <v>14741</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:24</t>
+          <t>2026-09-19 19:01:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5286493</v>
+        <v>4.5261617</v>
       </c>
       <c r="G5" t="n">
-        <v>26780</v>
+        <v>26785</v>
       </c>
       <c r="H5" t="n">
-        <v>9976</v>
+        <v>9979</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2049</v>
+        <v>2062</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>1836</v>
+        <v>1849</v>
       </c>
       <c r="R5" t="n">
-        <v>21749</v>
+        <v>21728</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:24</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.164835</v>
+        <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6110</v>
+        <v>6111</v>
       </c>
       <c r="H8" t="n">
         <v>2265</v>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R8" t="n">
-        <v>4520</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:01:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:25</t>
+          <t>2026-09-19 19:02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:26</t>
+          <t>2026-09-19 19:02:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:26</t>
+          <t>2026-09-19 19:02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5653906</v>
+        <v>4.551697</v>
       </c>
       <c r="G14" t="n">
-        <v>13674</v>
+        <v>13688</v>
       </c>
       <c r="H14" t="n">
-        <v>5081</v>
+        <v>5086</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1253</v>
+        <v>1284</v>
       </c>
       <c r="O14" t="n">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="P14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="R14" t="n">
-        <v>11907</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:26</t>
+          <t>2026-09-19 19:02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-18 19:16:27</t>
+          <t>2026-09-19 19:02:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1582,10 +1582,10 @@
         <v>4.691997</v>
       </c>
       <c r="G16" t="n">
-        <v>46753</v>
+        <v>46750</v>
       </c>
       <c r="H16" t="n">
-        <v>3000</v>
+        <v>3005</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>2353</v>
       </c>
       <c r="R16" t="n">
-        <v>40912</v>
+        <v>40909</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:58</t>
+          <t>2026-09-20 19:07:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:58</t>
+          <t>2026-09-20 19:07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4077425</v>
+        <v>4.4060693</v>
       </c>
       <c r="G3" t="n">
-        <v>31077</v>
+        <v>31085</v>
       </c>
       <c r="H3" t="n">
-        <v>9237</v>
+        <v>9241</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4080</v>
+        <v>4087</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25780</v>
+        <v>25772</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:58</t>
+          <t>2026-09-20 19:07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6028461</v>
+        <v>3.6037493</v>
       </c>
       <c r="G4" t="n">
-        <v>25129</v>
+        <v>25131</v>
       </c>
       <c r="H4" t="n">
         <v>5612</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7361</v>
+        <v>7358</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="Q4" t="n">
         <v>1266</v>
       </c>
       <c r="R4" t="n">
-        <v>14741</v>
+        <v>14749</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:58</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5261617</v>
+        <v>4.5256786</v>
       </c>
       <c r="G5" t="n">
-        <v>26785</v>
+        <v>26790</v>
       </c>
       <c r="H5" t="n">
-        <v>9979</v>
+        <v>9982</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="Q5" t="n">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="R5" t="n">
-        <v>21728</v>
+        <v>21733</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>6111</v>
       </c>
       <c r="H8" t="n">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 6, 2026</t>
+          <t>Sep 7, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8557692</v>
+        <v>3.883495</v>
       </c>
       <c r="G10" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H10" t="n">
         <v>246</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9.2</t>
+          <t>Varies with device</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1165,13 +1165,9 @@
           <t>May 5, 2024</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Jul 2, 2026</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1183,7 +1179,7 @@
         <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -1194,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-19 19:01:59</t>
+          <t>2026-09-20 19:07:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:00</t>
+          <t>2026-09-20 19:07:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:00</t>
+          <t>2026-09-20 19:07:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:00</t>
+          <t>2026-09-20 19:07:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1431,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.551697</v>
+        <v>4.5399685</v>
       </c>
       <c r="G14" t="n">
-        <v>13688</v>
+        <v>13699</v>
       </c>
       <c r="H14" t="n">
-        <v>5086</v>
+        <v>5089</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1463,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1284</v>
+        <v>1320</v>
       </c>
       <c r="O14" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="P14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R14" t="n">
-        <v>11861</v>
+        <v>11830</v>
       </c>
     </row>
     <row r="15">
@@ -1486,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:00</t>
+          <t>2026-09-20 19:07:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1560,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-19 19:02:01</t>
+          <t>2026-09-20 19:07:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1579,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.691997</v>
+        <v>4.69156</v>
       </c>
       <c r="G16" t="n">
-        <v>46750</v>
+        <v>46758</v>
       </c>
       <c r="H16" t="n">
-        <v>3005</v>
+        <v>3009</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1611,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2342</v>
+        <v>2338</v>
       </c>
       <c r="O16" t="n">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="P16" t="n">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="Q16" t="n">
-        <v>2353</v>
+        <v>2360</v>
       </c>
       <c r="R16" t="n">
-        <v>40909</v>
+        <v>40904</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:00</t>
+          <t>2026-09-21 20:41:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.01</v>
+        <v>4.009901</v>
       </c>
       <c r="G2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -588,10 +588,10 @@
         <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:00</t>
+          <t>2026-09-21 20:41:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4060693</v>
+        <v>4.402527</v>
       </c>
       <c r="G3" t="n">
-        <v>31085</v>
+        <v>31093</v>
       </c>
       <c r="H3" t="n">
-        <v>9241</v>
+        <v>9244</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4087</v>
+        <v>4107</v>
       </c>
       <c r="O3" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
         <v>279</v>
@@ -665,7 +665,7 @@
         <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25772</v>
+        <v>25749</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:00</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6037493</v>
+        <v>3.6023316</v>
       </c>
       <c r="G4" t="n">
-        <v>25131</v>
+        <v>25135</v>
       </c>
       <c r="H4" t="n">
         <v>5612</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7358</v>
+        <v>7373</v>
       </c>
       <c r="O4" t="n">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="Q4" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14749</v>
+        <v>14747</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5256786</v>
+        <v>4.527963</v>
       </c>
       <c r="G5" t="n">
-        <v>26790</v>
+        <v>26802</v>
       </c>
       <c r="H5" t="n">
-        <v>9982</v>
+        <v>9985</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2068</v>
+        <v>2045</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="Q5" t="n">
-        <v>1845</v>
+        <v>1856</v>
       </c>
       <c r="R5" t="n">
-        <v>21733</v>
+        <v>21745</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -887,7 +887,7 @@
         <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:01</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.883495</v>
+        <v>3.8846154</v>
       </c>
       <c r="G10" t="n">
         <v>573</v>
       </c>
       <c r="H10" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:02</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:02</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,10 +1286,10 @@
         <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
-        <v>4726</v>
+        <v>4727</v>
       </c>
       <c r="H12" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:02</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:02</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.5399685</v>
+        <v>4.530549</v>
       </c>
       <c r="G14" t="n">
-        <v>13699</v>
+        <v>13718</v>
       </c>
       <c r="H14" t="n">
-        <v>5089</v>
+        <v>5102</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.6.8</t>
+          <t>10.7.0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,23 +1455,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sep 14, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="O14" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q14" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="R14" t="n">
-        <v>11830</v>
+        <v>11818</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:02</t>
+          <t>2026-09-21 20:41:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3937</v>
       </c>
       <c r="H15" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1545,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-20 19:07:03</t>
+          <t>2026-09-21 20:41:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.69156</v>
+        <v>4.6909046</v>
       </c>
       <c r="G16" t="n">
-        <v>46758</v>
+        <v>46761</v>
       </c>
       <c r="H16" t="n">
-        <v>3009</v>
+        <v>3011</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2338</v>
+        <v>2347</v>
       </c>
       <c r="O16" t="n">
         <v>398</v>
@@ -1616,10 +1616,10 @@
         <v>752</v>
       </c>
       <c r="Q16" t="n">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="R16" t="n">
-        <v>40904</v>
+        <v>40901</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:28</t>
+          <t>2026-09-22 19:56:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.009901</v>
+        <v>4.04</v>
       </c>
       <c r="G2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2" t="n">
         <v>180</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:28</t>
+          <t>2026-09-22 19:56:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.402527</v>
+        <v>4.402386</v>
       </c>
       <c r="G3" t="n">
-        <v>31093</v>
+        <v>31108</v>
       </c>
       <c r="H3" t="n">
-        <v>9244</v>
+        <v>9250</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4107</v>
+        <v>4104</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25749</v>
+        <v>25754</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6023316</v>
+        <v>3.605042</v>
       </c>
       <c r="G4" t="n">
-        <v>25135</v>
+        <v>25138</v>
       </c>
       <c r="H4" t="n">
-        <v>5612</v>
+        <v>5614</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7373</v>
+        <v>7360</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="Q4" t="n">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="R4" t="n">
-        <v>14747</v>
+        <v>14770</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.527963</v>
+        <v>4.5310807</v>
       </c>
       <c r="G5" t="n">
-        <v>26802</v>
+        <v>26818</v>
       </c>
       <c r="H5" t="n">
-        <v>9985</v>
+        <v>9992</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2045</v>
+        <v>2024</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
@@ -810,10 +810,10 @@
         <v>849</v>
       </c>
       <c r="Q5" t="n">
-        <v>1856</v>
+        <v>1867</v>
       </c>
       <c r="R5" t="n">
-        <v>21745</v>
+        <v>21772</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6111</v>
+        <v>6112</v>
       </c>
       <c r="H8" t="n">
         <v>2266</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:29</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6371682</v>
+        <v>3.6725664</v>
       </c>
       <c r="G9" t="n">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H9" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8846154</v>
+        <v>3.8857143</v>
       </c>
       <c r="G10" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H10" t="n">
         <v>247</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7467701</v>
+        <v>2.7512953</v>
       </c>
       <c r="G12" t="n">
-        <v>4727</v>
+        <v>4728</v>
       </c>
       <c r="H12" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2405</v>
+        <v>2399</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1770</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.530549</v>
+        <v>4.514897</v>
       </c>
       <c r="G14" t="n">
-        <v>13718</v>
+        <v>13734</v>
       </c>
       <c r="H14" t="n">
-        <v>5102</v>
+        <v>5111</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1357</v>
+        <v>1416</v>
       </c>
       <c r="O14" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R14" t="n">
-        <v>11818</v>
+        <v>11782</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:30</t>
+          <t>2026-09-22 19:56:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4236312</v>
+        <v>3.4121037</v>
       </c>
       <c r="G15" t="n">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="H15" t="n">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1361</v>
+        <v>1372</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1545,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2188</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 20:41:31</t>
+          <t>2026-09-22 19:56:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6909046</v>
+        <v>4.691051</v>
       </c>
       <c r="G16" t="n">
         <v>46761</v>
       </c>
       <c r="H16" t="n">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="O16" t="n">
         <v>398</v>
       </c>
       <c r="P16" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="Q16" t="n">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="R16" t="n">
-        <v>40901</v>
+        <v>40903</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:20</t>
+          <t>2026-09-23 19:54:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.04</v>
+        <v>4.0495048</v>
       </c>
       <c r="G2" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2" t="n">
         <v>180</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:21</t>
+          <t>2026-09-23 19:55:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.402386</v>
+        <v>4.402452</v>
       </c>
       <c r="G3" t="n">
-        <v>31108</v>
+        <v>31117</v>
       </c>
       <c r="H3" t="n">
-        <v>9250</v>
+        <v>9253</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4104</v>
+        <v>4106</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25754</v>
+        <v>25763</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:21</t>
+          <t>2026-09-23 19:55:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.605042</v>
+        <v>3.5954692</v>
       </c>
       <c r="G4" t="n">
-        <v>25138</v>
+        <v>25142</v>
       </c>
       <c r="H4" t="n">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7360</v>
+        <v>7419</v>
       </c>
       <c r="O4" t="n">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="Q4" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="R4" t="n">
-        <v>14770</v>
+        <v>14709</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:21</t>
+          <t>2026-09-23 19:55:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5310807</v>
+        <v>4.52801</v>
       </c>
       <c r="G5" t="n">
-        <v>26818</v>
+        <v>26834</v>
       </c>
       <c r="H5" t="n">
-        <v>9992</v>
+        <v>9995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="P5" t="n">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="Q5" t="n">
-        <v>1867</v>
+        <v>1873</v>
       </c>
       <c r="R5" t="n">
-        <v>21772</v>
+        <v>21752</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:21</t>
+          <t>2026-09-23 19:55:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:21</t>
+          <t>2026-09-23 19:55:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,10 +994,10 @@
         <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6112</v>
+        <v>6111</v>
       </c>
       <c r="H8" t="n">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6725664</v>
+        <v>3.6548672</v>
       </c>
       <c r="G9" t="n">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H9" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 7, 2026</t>
+          <t>Sep 6, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.6817155</v>
       </c>
       <c r="G11" t="n">
-        <v>15007</v>
+        <v>15008</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1253,7 +1253,7 @@
         <v>824</v>
       </c>
       <c r="R11" t="n">
-        <v>13030</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4728</v>
       </c>
       <c r="H12" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:22</t>
+          <t>2026-09-23 19:55:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:23</t>
+          <t>2026-09-23 19:55:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.514897</v>
+        <v>4.4776</v>
       </c>
       <c r="G14" t="n">
-        <v>13734</v>
+        <v>13749</v>
       </c>
       <c r="H14" t="n">
         <v>5111</v>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1416</v>
+        <v>1528</v>
       </c>
       <c r="O14" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="R14" t="n">
-        <v>11782</v>
+        <v>11658</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:23</t>
+          <t>2026-09-23 19:55:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4121037</v>
+        <v>3.4109194</v>
       </c>
       <c r="G15" t="n">
         <v>3938</v>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
       </c>
       <c r="P15" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2178</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-22 19:56:23</t>
+          <t>2026-09-23 19:55:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.691051</v>
+        <v>4.689941</v>
       </c>
       <c r="G16" t="n">
-        <v>46761</v>
+        <v>46759</v>
       </c>
       <c r="H16" t="n">
-        <v>3012</v>
+        <v>3009</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="O16" t="n">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="P16" t="n">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="Q16" t="n">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="R16" t="n">
-        <v>40903</v>
+        <v>40892</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 19:54:59</t>
+          <t>2026-09-24 20:13:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.0495048</v>
+        <v>4.04</v>
       </c>
       <c r="G2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2" t="n">
         <v>180</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:00</t>
+          <t>2026-09-24 20:13:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.402452</v>
+        <v>4.396247</v>
       </c>
       <c r="G3" t="n">
-        <v>31117</v>
+        <v>31126</v>
       </c>
       <c r="H3" t="n">
-        <v>9253</v>
+        <v>9255</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4106</v>
+        <v>4156</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q3" t="n">
         <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25763</v>
+        <v>25722</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:00</t>
+          <t>2026-09-24 20:13:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5954692</v>
+        <v>3.5952072</v>
       </c>
       <c r="G4" t="n">
-        <v>25142</v>
+        <v>25144</v>
       </c>
       <c r="H4" t="n">
         <v>5615</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7419</v>
+        <v>7425</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="P4" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1268</v>
+        <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14709</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:00</t>
+          <t>2026-09-24 20:13:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.52801</v>
+        <v>4.5285773</v>
       </c>
       <c r="G5" t="n">
-        <v>26834</v>
+        <v>26849</v>
       </c>
       <c r="H5" t="n">
-        <v>9995</v>
+        <v>9997</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="O5" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P5" t="n">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="Q5" t="n">
-        <v>1873</v>
+        <v>1903</v>
       </c>
       <c r="R5" t="n">
         <v>21752</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:00</t>
+          <t>2026-09-24 20:13:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -875,19 +875,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
         <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:00</t>
+          <t>2026-09-24 20:13:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:01</t>
+          <t>2026-09-24 20:13:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:01</t>
+          <t>2026-09-24 20:13:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6548672</v>
+        <v>3.619469</v>
       </c>
       <c r="G9" t="n">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H9" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>813</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:01</t>
+          <t>2026-09-24 20:13:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96120</v>
+        <v>96121</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:01</t>
+          <t>2026-09-24 20:13:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:01</t>
+          <t>2026-09-24 20:13:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7512953</v>
+        <v>2.7409327</v>
       </c>
       <c r="G12" t="n">
-        <v>4728</v>
+        <v>4730</v>
       </c>
       <c r="H12" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2400</v>
+        <v>2413</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1775</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:02</t>
+          <t>2026-09-24 20:13:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:02</t>
+          <t>2026-09-24 20:13:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4776</v>
+        <v>4.474227</v>
       </c>
       <c r="G14" t="n">
-        <v>13749</v>
+        <v>13762</v>
       </c>
       <c r="H14" t="n">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="O14" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="P14" t="n">
         <v>108</v>
       </c>
       <c r="Q14" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R14" t="n">
-        <v>11658</v>
+        <v>11655</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:02</t>
+          <t>2026-09-24 20:13:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.4109194</v>
       </c>
       <c r="G15" t="n">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="H15" t="n">
         <v>1593</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>413364</v>
+        <v>413365</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-23 19:55:02</t>
+          <t>2026-09-24 20:13:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.689941</v>
+        <v>4.6873226</v>
       </c>
       <c r="G16" t="n">
-        <v>46759</v>
+        <v>46762</v>
       </c>
       <c r="H16" t="n">
-        <v>3009</v>
+        <v>3012</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2356</v>
+        <v>2388</v>
       </c>
       <c r="O16" t="n">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P16" t="n">
         <v>740</v>
       </c>
       <c r="Q16" t="n">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="R16" t="n">
-        <v>40892</v>
+        <v>40865</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:11</t>
+          <t>2026-09-25 20:10:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:11</t>
+          <t>2026-09-25 20:10:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.396247</v>
+        <v>4.397978</v>
       </c>
       <c r="G3" t="n">
-        <v>31126</v>
+        <v>31132</v>
       </c>
       <c r="H3" t="n">
-        <v>9255</v>
+        <v>9257</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4156</v>
+        <v>4148</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25722</v>
+        <v>25746</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:11</t>
+          <t>2026-09-25 20:10:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.5952072</v>
       </c>
       <c r="G4" t="n">
-        <v>25144</v>
+        <v>25142</v>
       </c>
       <c r="H4" t="n">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14720</v>
+        <v>14719</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:12</t>
+          <t>2026-09-25 20:10:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5285773</v>
+        <v>4.528404</v>
       </c>
       <c r="G5" t="n">
-        <v>26849</v>
+        <v>26858</v>
       </c>
       <c r="H5" t="n">
-        <v>9997</v>
+        <v>9998</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="O5" t="n">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="P5" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="Q5" t="n">
-        <v>1903</v>
+        <v>1929</v>
       </c>
       <c r="R5" t="n">
-        <v>21752</v>
+        <v>21741</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:12</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:12</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3318586</v>
+        <v>4.3171806</v>
       </c>
       <c r="G7" t="n">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="H7" t="n">
         <v>1162</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="O7" t="n">
         <v>55</v>
@@ -958,10 +958,10 @@
         <v>110</v>
       </c>
       <c r="Q7" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2476</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:13</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>6111</v>
       </c>
       <c r="H8" t="n">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:13</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.619469</v>
+        <v>3.5964913</v>
       </c>
       <c r="G9" t="n">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="H9" t="n">
         <v>541</v>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 6, 2026</t>
+          <t>Sep 7, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:13</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8857143</v>
+        <v>3.875</v>
       </c>
       <c r="G10" t="n">
         <v>575</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:14</t>
+          <t>2026-09-25 20:10:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:14</t>
+          <t>2026-09-25 20:10:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7409327</v>
+        <v>2.7467701</v>
       </c>
       <c r="G12" t="n">
-        <v>4730</v>
+        <v>4731</v>
       </c>
       <c r="H12" t="n">
         <v>1964</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2413</v>
+        <v>2408</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1763</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:14</t>
+          <t>2026-09-25 20:10:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:15</t>
+          <t>2026-09-25 20:10:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.474227</v>
+        <v>4.469146</v>
       </c>
       <c r="G14" t="n">
-        <v>13762</v>
+        <v>13766</v>
       </c>
       <c r="H14" t="n">
-        <v>5112</v>
+        <v>5115</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1527</v>
+        <v>1546</v>
       </c>
       <c r="O14" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R14" t="n">
-        <v>11655</v>
+        <v>11641</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:15</t>
+          <t>2026-09-25 20:10:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4109194</v>
+        <v>3.4063401</v>
       </c>
       <c r="G15" t="n">
-        <v>3939</v>
+        <v>3938</v>
       </c>
       <c r="H15" t="n">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1545,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2173</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 20:13:15</t>
+          <t>2026-09-25 20:10:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6873226</v>
+        <v>4.6856537</v>
       </c>
       <c r="G16" t="n">
-        <v>46762</v>
+        <v>46765</v>
       </c>
       <c r="H16" t="n">
         <v>3012</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2388</v>
+        <v>2408</v>
       </c>
       <c r="O16" t="n">
         <v>408</v>
       </c>
       <c r="P16" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q16" t="n">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="R16" t="n">
-        <v>40865</v>
+        <v>40851</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:31</t>
+          <t>2026-09-26 19:29:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:31</t>
+          <t>2026-09-26 19:29:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.397978</v>
+        <v>4.398339</v>
       </c>
       <c r="G3" t="n">
-        <v>31132</v>
+        <v>31137</v>
       </c>
       <c r="H3" t="n">
-        <v>9257</v>
+        <v>9258</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25746</v>
+        <v>25761</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:31</t>
+          <t>2026-09-26 19:29:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.5952072</v>
       </c>
       <c r="G4" t="n">
-        <v>25142</v>
+        <v>25143</v>
       </c>
       <c r="H4" t="n">
         <v>5616</v>
@@ -739,7 +739,7 @@
         <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14719</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:31</t>
+          <t>2026-09-26 19:29:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.528404</v>
+        <v>4.5281367</v>
       </c>
       <c r="G5" t="n">
-        <v>26858</v>
+        <v>26864</v>
       </c>
       <c r="H5" t="n">
-        <v>9998</v>
+        <v>9999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="O5" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="Q5" t="n">
-        <v>1929</v>
+        <v>1936</v>
       </c>
       <c r="R5" t="n">
-        <v>21741</v>
+        <v>21735</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -887,7 +887,7 @@
         <v>27</v>
       </c>
       <c r="R6" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6111</v>
+        <v>6113</v>
       </c>
       <c r="H8" t="n">
         <v>2266</v>
@@ -1032,10 +1032,10 @@
         <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>4526</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 7, 2026</t>
+          <t>Sep 6, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.875</v>
+        <v>3.8857143</v>
       </c>
       <c r="G10" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H10" t="n">
         <v>247</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:32</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.6817155</v>
       </c>
       <c r="G11" t="n">
-        <v>15008</v>
+        <v>15007</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1253,7 +1253,7 @@
         <v>824</v>
       </c>
       <c r="R11" t="n">
-        <v>13031</v>
+        <v>13030</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:33</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4731</v>
       </c>
       <c r="H12" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:33</t>
+          <t>2026-09-26 19:29:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7395833</v>
+        <v>2.7628865</v>
       </c>
       <c r="G13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H13" t="n">
         <v>41</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:33</t>
+          <t>2026-09-26 19:29:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.469146</v>
+        <v>4.4629335</v>
       </c>
       <c r="G14" t="n">
-        <v>13766</v>
+        <v>13769</v>
       </c>
       <c r="H14" t="n">
-        <v>5115</v>
+        <v>5116</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1546</v>
+        <v>1562</v>
       </c>
       <c r="O14" t="n">
         <v>216</v>
       </c>
       <c r="P14" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="Q14" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R14" t="n">
-        <v>11641</v>
+        <v>11618</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:33</t>
+          <t>2026-09-26 19:29:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-25 20:10:33</t>
+          <t>2026-09-26 19:29:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>46765</v>
       </c>
       <c r="H16" t="n">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>2354</v>
       </c>
       <c r="R16" t="n">
-        <v>40851</v>
+        <v>40850</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:47</t>
+          <t>2026-09-27 19:54:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>420</v>
       </c>
       <c r="H2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:48</t>
+          <t>2026-09-27 19:54:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.398339</v>
+        <v>4.398415</v>
       </c>
       <c r="G3" t="n">
-        <v>31137</v>
+        <v>31145</v>
       </c>
       <c r="H3" t="n">
-        <v>9258</v>
+        <v>9260</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2429952</v>
+        <v>2439250</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4148</v>
+        <v>4150</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25761</v>
+        <v>25770</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:48</t>
+          <t>2026-09-27 19:54:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5952072</v>
+        <v>3.5977979</v>
       </c>
       <c r="G4" t="n">
-        <v>25143</v>
+        <v>25145</v>
       </c>
       <c r="H4" t="n">
         <v>5616</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2633254</v>
+        <v>2638644</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7425</v>
+        <v>7408</v>
       </c>
       <c r="O4" t="n">
         <v>879</v>
@@ -739,7 +739,7 @@
         <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14720</v>
+        <v>14737</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:48</t>
+          <t>2026-09-27 19:54:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5281367</v>
+        <v>4.526096</v>
       </c>
       <c r="G5" t="n">
-        <v>26864</v>
+        <v>26867</v>
       </c>
       <c r="H5" t="n">
-        <v>9999</v>
+        <v>10006</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2025</v>
+        <v>2040</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Q5" t="n">
-        <v>1936</v>
+        <v>1928</v>
       </c>
       <c r="R5" t="n">
-        <v>21735</v>
+        <v>21728</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:48</t>
+          <t>2026-09-27 19:54:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:48</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>3147</v>
       </c>
       <c r="H7" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,10 +994,10 @@
         <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6113</v>
+        <v>6112</v>
       </c>
       <c r="H8" t="n">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,7 +1068,7 @@
         <v>3.5964913</v>
       </c>
       <c r="G9" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H9" t="n">
         <v>541</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7467701</v>
+        <v>2.742268</v>
       </c>
       <c r="G12" t="n">
-        <v>4731</v>
+        <v>4732</v>
       </c>
       <c r="H12" t="n">
         <v>1965</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2408</v>
+        <v>2414</v>
       </c>
       <c r="O12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P12" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>1771</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:49</t>
+          <t>2026-09-27 19:54:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:50</t>
+          <t>2026-09-27 19:54:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4629335</v>
+        <v>4.4610543</v>
       </c>
       <c r="G14" t="n">
-        <v>13769</v>
+        <v>13771</v>
       </c>
       <c r="H14" t="n">
         <v>5116</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1562</v>
+        <v>1570</v>
       </c>
       <c r="O14" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P14" t="n">
         <v>118</v>
@@ -1471,7 +1471,7 @@
         <v>248</v>
       </c>
       <c r="R14" t="n">
-        <v>11618</v>
+        <v>11613</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:50</t>
+          <t>2026-09-27 19:54:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4063401</v>
+        <v>3.3994253</v>
       </c>
       <c r="G15" t="n">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="H15" t="n">
         <v>1594</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="O15" t="n">
         <v>135</v>
@@ -1545,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2166</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26 19:29:51</t>
+          <t>2026-09-27 19:54:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6856537</v>
+        <v>4.6857142</v>
       </c>
       <c r="G16" t="n">
-        <v>46765</v>
+        <v>46768</v>
       </c>
       <c r="H16" t="n">
         <v>3013</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="O16" t="n">
         <v>408</v>
@@ -1616,10 +1616,10 @@
         <v>739</v>
       </c>
       <c r="Q16" t="n">
-        <v>2354</v>
+        <v>2363</v>
       </c>
       <c r="R16" t="n">
-        <v>40850</v>
+        <v>40848</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:54</t>
+          <t>2026-09-28 22:19:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.04</v>
+        <v>4.0495048</v>
       </c>
       <c r="G2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2" t="n">
         <v>181</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41296</v>
+        <v>41670</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:54</t>
+          <t>2026-09-28 22:19:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.398415</v>
+        <v>4.396751</v>
       </c>
       <c r="G3" t="n">
-        <v>31145</v>
+        <v>31155</v>
       </c>
       <c r="H3" t="n">
-        <v>9260</v>
+        <v>9265</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4150</v>
+        <v>4160</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25770</v>
+        <v>25755</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:54</t>
+          <t>2026-09-28 22:19:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5977979</v>
+        <v>3.5952072</v>
       </c>
       <c r="G4" t="n">
-        <v>25145</v>
+        <v>25142</v>
       </c>
       <c r="H4" t="n">
         <v>5616</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7408</v>
+        <v>7424</v>
       </c>
       <c r="O4" t="n">
         <v>879</v>
@@ -739,7 +739,7 @@
         <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14737</v>
+        <v>14718</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:54</t>
+          <t>2026-09-28 22:19:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.526096</v>
+        <v>4.5264473</v>
       </c>
       <c r="G5" t="n">
-        <v>26867</v>
+        <v>26886</v>
       </c>
       <c r="H5" t="n">
-        <v>10006</v>
+        <v>10012</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>682142</v>
+        <v>685743</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2040</v>
+        <v>2026</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="P5" t="n">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="Q5" t="n">
-        <v>1928</v>
+        <v>1914</v>
       </c>
       <c r="R5" t="n">
-        <v>21728</v>
+        <v>21745</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:54</t>
+          <t>2026-09-28 22:19:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112615</v>
+        <v>112921</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>4.0.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 9, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3171806</v>
+        <v>4.3201756</v>
       </c>
       <c r="G7" t="n">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="H7" t="n">
         <v>1163</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>458165</v>
+        <v>459250</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q7" t="n">
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2466</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>4.1691175</v>
       </c>
       <c r="G8" t="n">
-        <v>6112</v>
+        <v>6114</v>
       </c>
       <c r="H8" t="n">
         <v>2267</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>466867</v>
+        <v>471351</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>4527</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>183566</v>
+        <v>184236</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8857143</v>
+        <v>3.9134614</v>
       </c>
       <c r="G10" t="n">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96121</v>
+        <v>96745</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>276075</v>
+        <v>276731</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:55</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>359442</v>
+        <v>360213</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:56</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22345</v>
+        <v>22387</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:56</t>
+          <t>2026-09-28 22:19:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4610543</v>
+        <v>4.458759</v>
       </c>
       <c r="G14" t="n">
-        <v>13771</v>
+        <v>13773</v>
       </c>
       <c r="H14" t="n">
-        <v>5116</v>
+        <v>5122</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1290305</v>
+        <v>1297513</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.7.0</t>
+          <t>10.7.1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 27, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="O14" t="n">
         <v>215</v>
@@ -1471,7 +1471,7 @@
         <v>248</v>
       </c>
       <c r="R14" t="n">
-        <v>11613</v>
+        <v>11608</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:56</t>
+          <t>2026-09-28 22:19:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>413365</v>
+        <v>416029</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-27 19:54:56</t>
+          <t>2026-09-28 22:19:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6857142</v>
+        <v>4.6858625</v>
       </c>
       <c r="G16" t="n">
-        <v>46768</v>
+        <v>46772</v>
       </c>
       <c r="H16" t="n">
-        <v>3013</v>
+        <v>3015</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>593003</v>
+        <v>596341</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="O16" t="n">
         <v>408</v>
@@ -1616,10 +1616,10 @@
         <v>739</v>
       </c>
       <c r="Q16" t="n">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="R16" t="n">
-        <v>40848</v>
+        <v>40854</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:10</t>
+          <t>2026-09-29 21:06:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>421</v>
       </c>
       <c r="H2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:10</t>
+          <t>2026-09-29 21:06:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.396751</v>
+        <v>4.395818</v>
       </c>
       <c r="G3" t="n">
-        <v>31155</v>
+        <v>31160</v>
       </c>
       <c r="H3" t="n">
-        <v>9265</v>
+        <v>9271</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2439250</v>
+        <v>2441667</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4160</v>
+        <v>4166</v>
       </c>
       <c r="O3" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="R3" t="n">
-        <v>25755</v>
+        <v>25745</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:10</t>
+          <t>2026-09-29 21:06:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.5952072</v>
       </c>
       <c r="G4" t="n">
-        <v>25142</v>
+        <v>25143</v>
       </c>
       <c r="H4" t="n">
         <v>5616</v>
@@ -739,7 +739,7 @@
         <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14718</v>
+        <v>14719</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:11</t>
+          <t>2026-09-29 21:06:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5264473</v>
+        <v>4.52794</v>
       </c>
       <c r="G5" t="n">
-        <v>26886</v>
+        <v>26895</v>
       </c>
       <c r="H5" t="n">
-        <v>10012</v>
+        <v>10016</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="O5" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="Q5" t="n">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="R5" t="n">
-        <v>21745</v>
+        <v>21757</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:11</t>
+          <t>2026-09-29 21:06:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:11</t>
+          <t>2026-09-29 21:06:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.3201756</v>
       </c>
       <c r="G7" t="n">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="H7" t="n">
         <v>1163</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>459250</v>
+        <v>459560</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2470</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:11</t>
+          <t>2026-09-29 21:06:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1691175</v>
+        <v>4.1706424</v>
       </c>
       <c r="G8" t="n">
-        <v>6114</v>
+        <v>6113</v>
       </c>
       <c r="H8" t="n">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4528</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1299</v>
       </c>
       <c r="H9" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 6, 2026</t>
+          <t>Sep 7, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:12</t>
+          <t>2026-09-29 21:06:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.458759</v>
+        <v>4.4501557</v>
       </c>
       <c r="G14" t="n">
-        <v>13773</v>
+        <v>13784</v>
       </c>
       <c r="H14" t="n">
-        <v>5122</v>
+        <v>5126</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.7.1</t>
+          <t>10.7.2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,23 +1455,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sep 27, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1579</v>
+        <v>1610</v>
       </c>
       <c r="O14" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q14" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="R14" t="n">
-        <v>11608</v>
+        <v>11582</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:13</t>
+          <t>2026-09-29 21:06:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28 22:19:13</t>
+          <t>2026-09-29 21:06:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6858625</v>
+        <v>4.685937</v>
       </c>
       <c r="G16" t="n">
-        <v>46772</v>
+        <v>46773</v>
       </c>
       <c r="H16" t="n">
         <v>3015</v>
@@ -1613,13 +1613,13 @@
         <v>408</v>
       </c>
       <c r="P16" t="n">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q16" t="n">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="R16" t="n">
-        <v>40854</v>
+        <v>40856</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:46</t>
+          <t>2026-09-30 21:05:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.0495048</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2" t="n">
         <v>182</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41670</v>
+        <v>41797</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:46</t>
+          <t>2026-09-30 21:05:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.395818</v>
+        <v>4.391931</v>
       </c>
       <c r="G3" t="n">
-        <v>31160</v>
+        <v>31177</v>
       </c>
       <c r="H3" t="n">
-        <v>9271</v>
+        <v>9273</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2441667</v>
+        <v>2442900</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.2</t>
+          <t>4.46.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4166</v>
+        <v>4199</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>650</v>
       </c>
       <c r="R3" t="n">
-        <v>25745</v>
+        <v>25729</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:46</t>
+          <t>2026-09-30 21:05:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -684,62 +684,34 @@
           <t>com.arabbank.arabimobilev2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Arabi-Mobile</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Mobile App Conduct your banking transactions securely and on the go!</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3.5952072</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25143</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5616</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1,000,000+</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2638644</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Jul 2, 2018</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Sep 2, 2026</t>
-        </is>
-      </c>
+          <t>Varies with device</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>7424</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>879</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>862</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1253</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>14719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +722,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:47</t>
+          <t>2026-09-30 21:05:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +741,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.52794</v>
+        <v>4.527061</v>
       </c>
       <c r="G5" t="n">
-        <v>26895</v>
+        <v>26911</v>
       </c>
       <c r="H5" t="n">
-        <v>10016</v>
+        <v>10024</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +755,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>685743</v>
+        <v>686838</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +773,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2018</v>
+        <v>2027</v>
       </c>
       <c r="O5" t="n">
         <v>301</v>
       </c>
       <c r="P5" t="n">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q5" t="n">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="R5" t="n">
-        <v>21757</v>
+        <v>21767</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +796,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:47</t>
+          <t>2026-09-30 21:05:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +829,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>112921</v>
+        <v>113025</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +870,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:47</t>
+          <t>2026-09-30 21:05:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +944,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:47</t>
+          <t>2026-09-30 21:05:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +963,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1706424</v>
+        <v>4.172161</v>
       </c>
       <c r="G8" t="n">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="H8" t="n">
         <v>2268</v>
@@ -1005,7 +977,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>471351</v>
+        <v>472433</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +995,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="O8" t="n">
         <v>156</v>
@@ -1035,7 +1007,7 @@
         <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4530</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1018,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:48</t>
+          <t>2026-09-30 21:05:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1037,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5964913</v>
+        <v>3.5614035</v>
       </c>
       <c r="G9" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H9" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1051,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>184236</v>
+        <v>184464</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1069,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1109,7 +1081,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1092,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:48</t>
+          <t>2026-09-30 21:05:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1125,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96745</v>
+        <v>96923</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1162,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:48</t>
+          <t>2026-09-30 21:05:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1184,7 @@
         <v>4.6817155</v>
       </c>
       <c r="G11" t="n">
-        <v>15007</v>
+        <v>15006</v>
       </c>
       <c r="H11" t="n">
         <v>703</v>
@@ -1223,7 +1195,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>276731</v>
+        <v>276946</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1253,7 +1225,7 @@
         <v>824</v>
       </c>
       <c r="R11" t="n">
-        <v>13030</v>
+        <v>13029</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1236,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:48</t>
+          <t>2026-09-30 21:05:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1269,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>360213</v>
+        <v>360492</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1306,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:49</t>
+          <t>2026-09-30 21:05:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1339,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22387</v>
+        <v>22408</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1380,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:49</t>
+          <t>2026-09-30 21:05:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1399,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4501557</v>
+        <v>4.44751</v>
       </c>
       <c r="G14" t="n">
-        <v>13784</v>
+        <v>13803</v>
       </c>
       <c r="H14" t="n">
-        <v>5126</v>
+        <v>5133</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1413,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1297513</v>
+        <v>1299826</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1431,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="O14" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P14" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="Q14" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="R14" t="n">
-        <v>11582</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1454,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:49</t>
+          <t>2026-09-30 21:05:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1479,7 @@
         <v>3939</v>
       </c>
       <c r="H15" t="n">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,11 +1487,11 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>416029</v>
+        <v>416764</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1529,7 +1501,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Sep 12, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1528,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 21:06:49</t>
+          <t>2026-09-30 21:05:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1547,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.685937</v>
+        <v>4.6860847</v>
       </c>
       <c r="G16" t="n">
-        <v>46773</v>
+        <v>46775</v>
       </c>
       <c r="H16" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1561,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>596341</v>
+        <v>597395</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1579,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="O16" t="n">
         <v>408</v>
@@ -1616,10 +1588,10 @@
         <v>738</v>
       </c>
       <c r="Q16" t="n">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="R16" t="n">
-        <v>40856</v>
+        <v>40861</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:11</t>
+          <t>2026-10-01 21:26:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.05</v>
       </c>
       <c r="G2" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2" t="n">
         <v>182</v>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:11</t>
+          <t>2026-10-01 21:26:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.391931</v>
+        <v>4.3922415</v>
       </c>
       <c r="G3" t="n">
-        <v>31177</v>
+        <v>31188</v>
       </c>
       <c r="H3" t="n">
-        <v>9273</v>
+        <v>9275</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Oct 1, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4199</v>
+        <v>4200</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="R3" t="n">
-        <v>25729</v>
+        <v>25743</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:21</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -684,34 +684,62 @@
           <t>com.arabbank.arabimobilev2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arabi-Mobile</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mobile App Conduct your banking transactions securely and on the go!</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3.5968993</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25155</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5619</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1,000,000+</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2640239</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Varies with device</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>2.22.2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Jul 2, 2018</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sep 2, 2026</t>
+        </is>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7409</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>14722</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:21</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -741,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.527061</v>
+        <v>4.525508</v>
       </c>
       <c r="G5" t="n">
-        <v>26911</v>
+        <v>26938</v>
       </c>
       <c r="H5" t="n">
-        <v>10024</v>
+        <v>10027</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -773,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="O5" t="n">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="P5" t="n">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="Q5" t="n">
-        <v>1914</v>
+        <v>1932</v>
       </c>
       <c r="R5" t="n">
-        <v>21767</v>
+        <v>21764</v>
       </c>
     </row>
     <row r="6">
@@ -796,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:21</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -870,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:25</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -892,7 +920,7 @@
         <v>4.3201756</v>
       </c>
       <c r="G7" t="n">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="H7" t="n">
         <v>1163</v>
@@ -903,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>459560</v>
+        <v>459753</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -933,7 +961,7 @@
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2471</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="8">
@@ -944,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:26</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -963,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.172161</v>
+        <v>4.1798167</v>
       </c>
       <c r="G8" t="n">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="H8" t="n">
         <v>2268</v>
@@ -995,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4536</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="9">
@@ -1018,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:26</t>
+          <t>2026-10-01 21:26:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1040,7 +1068,7 @@
         <v>3.5614035</v>
       </c>
       <c r="G9" t="n">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H9" t="n">
         <v>543</v>
@@ -1092,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:26</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1111,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9134614</v>
+        <v>3.9238095</v>
       </c>
       <c r="G10" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H10" t="n">
         <v>246</v>
@@ -1139,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1151,7 +1179,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -1162,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:26</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1187,7 +1215,7 @@
         <v>15006</v>
       </c>
       <c r="H11" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1236,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:26</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1306,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:27</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1380,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:27</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1399,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.44751</v>
+        <v>4.4433537</v>
       </c>
       <c r="G14" t="n">
-        <v>13803</v>
+        <v>13824</v>
       </c>
       <c r="H14" t="n">
-        <v>5133</v>
+        <v>5139</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1431,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1617</v>
+        <v>1638</v>
       </c>
       <c r="O14" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P14" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q14" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="R14" t="n">
-        <v>11581</v>
+        <v>11589</v>
       </c>
     </row>
     <row r="15">
@@ -1454,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:27</t>
+          <t>2026-10-01 21:26:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1476,10 +1504,10 @@
         <v>3.3994253</v>
       </c>
       <c r="G15" t="n">
-        <v>3939</v>
+        <v>3941</v>
       </c>
       <c r="H15" t="n">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1487,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>416764</v>
+        <v>417643</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1517,7 +1545,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2161</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="16">
@@ -1528,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30 21:05:27</t>
+          <t>2026-10-01 21:26:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1547,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6860847</v>
+        <v>4.68529</v>
       </c>
       <c r="G16" t="n">
-        <v>46775</v>
+        <v>46774</v>
       </c>
       <c r="H16" t="n">
-        <v>3017</v>
+        <v>3021</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1561,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>597395</v>
+        <v>598073</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1579,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="O16" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="P16" t="n">
         <v>738</v>
       </c>
       <c r="Q16" t="n">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="R16" t="n">
-        <v>40861</v>
+        <v>40841</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:51</t>
+          <t>2026-10-02 21:04:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41797</v>
+        <v>41867</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:51</t>
+          <t>2026-10-02 21:04:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3922415</v>
+        <v>4.392023</v>
       </c>
       <c r="G3" t="n">
-        <v>31188</v>
+        <v>31200</v>
       </c>
       <c r="H3" t="n">
-        <v>9275</v>
+        <v>9280</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4200</v>
+        <v>4203</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -665,7 +665,7 @@
         <v>649</v>
       </c>
       <c r="R3" t="n">
-        <v>25743</v>
+        <v>25750</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5968993</v>
+        <v>3.5987055</v>
       </c>
       <c r="G4" t="n">
-        <v>25155</v>
+        <v>25164</v>
       </c>
       <c r="H4" t="n">
-        <v>5619</v>
+        <v>5621</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2640239</v>
+        <v>2641054</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7409</v>
+        <v>7393</v>
       </c>
       <c r="O4" t="n">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="P4" t="n">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1266</v>
+        <v>1237</v>
       </c>
       <c r="R4" t="n">
-        <v>14722</v>
+        <v>14755</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.525508</v>
+        <v>4.52474</v>
       </c>
       <c r="G5" t="n">
-        <v>26938</v>
+        <v>26952</v>
       </c>
       <c r="H5" t="n">
-        <v>10027</v>
+        <v>10031</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>686838</v>
+        <v>688055</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2021</v>
+        <v>2028</v>
       </c>
       <c r="O5" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="Q5" t="n">
-        <v>1932</v>
+        <v>1949</v>
       </c>
       <c r="R5" t="n">
-        <v>21764</v>
+        <v>21762</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113025</v>
+        <v>113099</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
         <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>472433</v>
+        <v>473003</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:52</t>
+          <t>2026-10-02 21:04:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>184464</v>
+        <v>184571</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96923</v>
+        <v>97041</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6817155</v>
+        <v>4.6799397</v>
       </c>
       <c r="G11" t="n">
-        <v>15006</v>
+        <v>15008</v>
       </c>
       <c r="H11" t="n">
         <v>704</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>276946</v>
+        <v>277074</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="R11" t="n">
-        <v>13029</v>
+        <v>13022</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.742268</v>
+        <v>2.7409327</v>
       </c>
       <c r="G12" t="n">
         <v>4732</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>360492</v>
+        <v>360653</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1314,16 +1314,16 @@
         <v>2414</v>
       </c>
       <c r="O12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1768</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7628865</v>
+        <v>2.78125</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22408</v>
+        <v>22418</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4433537</v>
+        <v>4.4084396</v>
       </c>
       <c r="G14" t="n">
-        <v>13824</v>
+        <v>13830</v>
       </c>
       <c r="H14" t="n">
-        <v>5139</v>
+        <v>5144</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1299826</v>
+        <v>1301055</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1638</v>
+        <v>1738</v>
       </c>
       <c r="O14" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="P14" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="Q14" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="R14" t="n">
-        <v>11589</v>
+        <v>11450</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:53</t>
+          <t>2026-10-02 21:04:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3994253</v>
+        <v>3.4085715</v>
       </c>
       <c r="G15" t="n">
-        <v>3941</v>
+        <v>3945</v>
       </c>
       <c r="H15" t="n">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="O15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2162</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-01 21:26:54</t>
+          <t>2026-10-02 21:04:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.68529</v>
+        <v>4.682996</v>
       </c>
       <c r="G16" t="n">
-        <v>46774</v>
+        <v>46777</v>
       </c>
       <c r="H16" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2403</v>
+        <v>2423</v>
       </c>
       <c r="O16" t="n">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="P16" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q16" t="n">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="R16" t="n">
-        <v>40841</v>
+        <v>40816</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:51</t>
+          <t>2026-10-03 19:34:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:51</t>
+          <t>2026-10-03 19:34:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.392023</v>
+        <v>4.3894887</v>
       </c>
       <c r="G3" t="n">
-        <v>31200</v>
+        <v>31206</v>
       </c>
       <c r="H3" t="n">
-        <v>9280</v>
+        <v>9283</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4203</v>
+        <v>4223</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R3" t="n">
-        <v>25750</v>
+        <v>25734</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:51</t>
+          <t>2026-10-03 19:34:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5987055</v>
+        <v>3.599612</v>
       </c>
       <c r="G4" t="n">
-        <v>25164</v>
+        <v>25166</v>
       </c>
       <c r="H4" t="n">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7393</v>
+        <v>7390</v>
       </c>
       <c r="O4" t="n">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="R4" t="n">
-        <v>14755</v>
+        <v>14763</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:52</t>
+          <t>2026-10-03 19:34:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.52474</v>
+        <v>4.525923</v>
       </c>
       <c r="G5" t="n">
-        <v>26952</v>
+        <v>26959</v>
       </c>
       <c r="H5" t="n">
         <v>10031</v>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="O5" t="n">
         <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="Q5" t="n">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="R5" t="n">
-        <v>21762</v>
+        <v>21781</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:52</t>
+          <t>2026-10-03 19:34:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:52</t>
+          <t>2026-10-03 19:34:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:52</t>
+          <t>2026-10-03 19:34:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1798167</v>
+        <v>4.1813188</v>
       </c>
       <c r="G8" t="n">
-        <v>6119</v>
+        <v>6121</v>
       </c>
       <c r="H8" t="n">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4558</v>
+        <v>4562</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:52</t>
+          <t>2026-10-03 19:34:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5614035</v>
+        <v>3.5350878</v>
       </c>
       <c r="G9" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H9" t="n">
         <v>543</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="P9" t="n">
         <v>11</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9238095</v>
+        <v>3.8962264</v>
       </c>
       <c r="G10" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H10" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6799397</v>
+        <v>4.68018</v>
       </c>
       <c r="G11" t="n">
-        <v>15008</v>
+        <v>15009</v>
       </c>
       <c r="H11" t="n">
         <v>704</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O11" t="n">
         <v>123</v>
@@ -1250,10 +1250,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R11" t="n">
-        <v>13022</v>
+        <v>13025</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4084396</v>
+        <v>4.398574</v>
       </c>
       <c r="G14" t="n">
-        <v>13830</v>
+        <v>13835</v>
       </c>
       <c r="H14" t="n">
-        <v>5144</v>
+        <v>5146</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1738</v>
+        <v>1775</v>
       </c>
       <c r="O14" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P14" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q14" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R14" t="n">
-        <v>11450</v>
+        <v>11422</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:53</t>
+          <t>2026-10-03 19:34:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4085715</v>
+        <v>3.4176137</v>
       </c>
       <c r="G15" t="n">
-        <v>3945</v>
+        <v>3947</v>
       </c>
       <c r="H15" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="O15" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P15" t="n">
         <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R15" t="n">
-        <v>2175</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 21:04:54</t>
+          <t>2026-10-03 19:34:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.682996</v>
+        <v>4.682921</v>
       </c>
       <c r="G16" t="n">
-        <v>46777</v>
+        <v>46775</v>
       </c>
       <c r="H16" t="n">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>737</v>
       </c>
       <c r="Q16" t="n">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="R16" t="n">
-        <v>40816</v>
+        <v>40813</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:12</t>
+          <t>2026-10-04 19:50:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>41867</v>
+        <v>42180</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:12</t>
+          <t>2026-10-04 19:50:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3894887</v>
+        <v>4.392947</v>
       </c>
       <c r="G3" t="n">
-        <v>31206</v>
+        <v>31219</v>
       </c>
       <c r="H3" t="n">
-        <v>9283</v>
+        <v>9286</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2442900</v>
+        <v>2449133</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4223</v>
+        <v>4200</v>
       </c>
       <c r="O3" t="n">
         <v>313</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25734</v>
+        <v>25781</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:12</t>
+          <t>2026-10-04 19:50:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.599612</v>
+        <v>3.5979314</v>
       </c>
       <c r="G4" t="n">
-        <v>25166</v>
+        <v>25169</v>
       </c>
       <c r="H4" t="n">
-        <v>5622</v>
+        <v>5624</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2641054</v>
+        <v>2645243</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7390</v>
+        <v>7402</v>
       </c>
       <c r="O4" t="n">
         <v>893</v>
@@ -739,7 +739,7 @@
         <v>1235</v>
       </c>
       <c r="R4" t="n">
-        <v>14763</v>
+        <v>14756</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:12</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.525923</v>
+        <v>4.526009</v>
       </c>
       <c r="G5" t="n">
-        <v>26959</v>
+        <v>26960</v>
       </c>
       <c r="H5" t="n">
-        <v>10031</v>
+        <v>10038</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>688055</v>
+        <v>689778</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P5" t="n">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="Q5" t="n">
-        <v>1945</v>
+        <v>1951</v>
       </c>
       <c r="R5" t="n">
-        <v>21781</v>
+        <v>21776</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:13</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113099</v>
+        <v>113306</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:13</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3201756</v>
+        <v>4.3171806</v>
       </c>
       <c r="G7" t="n">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="H7" t="n">
-        <v>1163</v>
+        <v>1177</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,11 +931,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>459753</v>
+        <v>460561</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>5.1.3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -945,11 +945,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Oct 1, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O7" t="n">
         <v>54</v>
@@ -961,7 +961,7 @@
         <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>2470</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:13</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1813188</v>
+        <v>4.177331</v>
       </c>
       <c r="G8" t="n">
-        <v>6121</v>
+        <v>6123</v>
       </c>
       <c r="H8" t="n">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>473003</v>
+        <v>476470</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P8" t="n">
         <v>178</v>
@@ -1035,7 +1035,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4562</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:13</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1071,7 +1071,7 @@
         <v>1302</v>
       </c>
       <c r="H9" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>184571</v>
+        <v>185108</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:13</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>3.8962264</v>
       </c>
       <c r="G10" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H10" t="n">
         <v>247</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>97041</v>
+        <v>97504</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:14</t>
+          <t>2026-10-04 19:50:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.68018</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
         <v>15009</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>277074</v>
+        <v>277692</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
         <v>123</v>
@@ -1253,7 +1253,7 @@
         <v>821</v>
       </c>
       <c r="R11" t="n">
-        <v>13025</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:14</t>
+          <t>2026-10-04 19:50:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4732</v>
       </c>
       <c r="H12" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>360653</v>
+        <v>361293</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:14</t>
+          <t>2026-10-04 19:50:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22418</v>
+        <v>22467</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:14</t>
+          <t>2026-10-04 19:50:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.398574</v>
+        <v>4.3968377</v>
       </c>
       <c r="G14" t="n">
-        <v>13835</v>
+        <v>13840</v>
       </c>
       <c r="H14" t="n">
         <v>5146</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1301055</v>
+        <v>1306858</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="O14" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="P14" t="n">
         <v>141</v>
       </c>
       <c r="Q14" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="R14" t="n">
-        <v>11422</v>
+        <v>11410</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:14</t>
+          <t>2026-10-04 19:50:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4176137</v>
+        <v>3.387931</v>
       </c>
       <c r="G15" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="H15" t="n">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>417643</v>
+        <v>419016</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1367</v>
+        <v>1394</v>
       </c>
       <c r="O15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2186</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-03 19:34:15</t>
+          <t>2026-10-04 19:50:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.682921</v>
+        <v>4.6825247</v>
       </c>
       <c r="G16" t="n">
-        <v>46775</v>
+        <v>46777</v>
       </c>
       <c r="H16" t="n">
         <v>3023</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>598073</v>
+        <v>601016</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>429</v>
       </c>
       <c r="P16" t="n">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="Q16" t="n">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="R16" t="n">
-        <v>40813</v>
+        <v>40805</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:34</t>
+          <t>2026-10-05 22:57:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42180</v>
+        <v>42188</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:34</t>
+          <t>2026-10-05 22:57:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.392947</v>
+        <v>4.3930883</v>
       </c>
       <c r="G3" t="n">
-        <v>31219</v>
+        <v>31226</v>
       </c>
       <c r="H3" t="n">
         <v>9286</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2449133</v>
+        <v>2449220</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4200</v>
+        <v>4191</v>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25781</v>
+        <v>25784</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:34</t>
+          <t>2026-10-05 22:57:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5979314</v>
+        <v>3.599612</v>
       </c>
       <c r="G4" t="n">
-        <v>25169</v>
+        <v>25173</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2645243</v>
+        <v>2645285</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.22.2</t>
+          <t>2.22.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -723,23 +723,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Sep 2, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7402</v>
+        <v>7392</v>
       </c>
       <c r="O4" t="n">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="R4" t="n">
-        <v>14756</v>
+        <v>14767</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.526009</v>
+        <v>4.526578</v>
       </c>
       <c r="G5" t="n">
-        <v>26960</v>
+        <v>26973</v>
       </c>
       <c r="H5" t="n">
         <v>10038</v>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>689778</v>
+        <v>689819</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>406.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Sep 14, 2026</t>
+          <t>Oct 2, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="O5" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P5" t="n">
-        <v>886</v>
+        <v>917</v>
       </c>
       <c r="Q5" t="n">
-        <v>1951</v>
+        <v>1937</v>
       </c>
       <c r="R5" t="n">
-        <v>21776</v>
+        <v>21785</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3171806</v>
+        <v>4.1894274</v>
       </c>
       <c r="G7" t="n">
-        <v>3147</v>
+        <v>3186</v>
       </c>
       <c r="H7" t="n">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>460561</v>
+        <v>460565</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="O7" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="P7" t="n">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="Q7" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="R7" t="n">
-        <v>2466</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177331</v>
+        <v>4.177982</v>
       </c>
       <c r="G8" t="n">
-        <v>6123</v>
+        <v>6124</v>
       </c>
       <c r="H8" t="n">
         <v>2270</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>476470</v>
+        <v>476516</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="O8" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4555</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1068,10 +1068,10 @@
         <v>3.5350878</v>
       </c>
       <c r="G9" t="n">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="H9" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185108</v>
+        <v>185114</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.8.1GMS</t>
+          <t>1.8.2GMS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sep 7, 2026</t>
+          <t>Oct 4, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>97504</v>
+        <v>97510</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:35</t>
+          <t>2026-10-05 22:57:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.677177</v>
       </c>
       <c r="G11" t="n">
-        <v>15009</v>
+        <v>15008</v>
       </c>
       <c r="H11" t="n">
         <v>704</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>277692</v>
+        <v>277697</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>821</v>
       </c>
       <c r="R11" t="n">
-        <v>13015</v>
+        <v>13013</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:36</t>
+          <t>2026-10-05 22:57:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4732</v>
       </c>
       <c r="H12" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>361293</v>
+        <v>361298</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:36</t>
+          <t>2026-10-05 22:57:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:36</t>
+          <t>2026-10-05 22:57:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3968377</v>
+        <v>4.39168</v>
       </c>
       <c r="G14" t="n">
-        <v>13840</v>
+        <v>13850</v>
       </c>
       <c r="H14" t="n">
-        <v>5146</v>
+        <v>5152</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1306858</v>
+        <v>1306926</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1771</v>
+        <v>1793</v>
       </c>
       <c r="O14" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P14" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q14" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R14" t="n">
-        <v>11410</v>
+        <v>11403</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:36</t>
+          <t>2026-10-05 22:57:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.387931</v>
+        <v>3.397143</v>
       </c>
       <c r="G15" t="n">
-        <v>3948</v>
+        <v>3950</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>419016</v>
+        <v>419045</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="O15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2154</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-04 19:50:36</t>
+          <t>2026-10-05 22:57:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>46777</v>
       </c>
       <c r="H16" t="n">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>601016</v>
+        <v>601052</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:49</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>423</v>
       </c>
       <c r="H2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:49</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3930883</v>
+        <v>4.3920865</v>
       </c>
       <c r="G3" t="n">
-        <v>31226</v>
+        <v>31230</v>
       </c>
       <c r="H3" t="n">
-        <v>9286</v>
+        <v>9288</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4191</v>
+        <v>4200</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25784</v>
+        <v>25780</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:50</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.599612</v>
+        <v>3.600517</v>
       </c>
       <c r="G4" t="n">
-        <v>25173</v>
+        <v>25178</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2645285</v>
+        <v>2647429</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7392</v>
+        <v>7388</v>
       </c>
       <c r="O4" t="n">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="R4" t="n">
-        <v>14767</v>
+        <v>14777</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:50</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.526578</v>
+        <v>4.5232368</v>
       </c>
       <c r="G5" t="n">
-        <v>26973</v>
+        <v>26980</v>
       </c>
       <c r="H5" t="n">
-        <v>10038</v>
+        <v>10041</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="O5" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="P5" t="n">
         <v>917</v>
       </c>
       <c r="Q5" t="n">
-        <v>1937</v>
+        <v>1913</v>
       </c>
       <c r="R5" t="n">
         <v>21785</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:50</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H6" t="n">
         <v>166</v>
@@ -871,11 +871,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:51</t>
+          <t>2026-10-06 21:19:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1894274</v>
+        <v>4.186147</v>
       </c>
       <c r="G7" t="n">
-        <v>3186</v>
+        <v>3191</v>
       </c>
       <c r="H7" t="n">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="O7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P7" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q7" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R7" t="n">
-        <v>2328</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:51</t>
+          <t>2026-10-06 21:20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -994,10 +994,10 @@
         <v>4.177982</v>
       </c>
       <c r="G8" t="n">
-        <v>6124</v>
+        <v>6125</v>
       </c>
       <c r="H8" t="n">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:51</t>
+          <t>2026-10-06 21:20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5350878</v>
+        <v>3.652174</v>
       </c>
       <c r="G9" t="n">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="H9" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185114</v>
+        <v>185402</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Oct 4, 2026</t>
+          <t>Oct 5, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="O9" t="n">
         <v>68</v>
@@ -1109,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>777</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:52</t>
+          <t>2026-10-06 21:20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:52</t>
+          <t>2026-10-06 21:20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677177</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>15008</v>
+        <v>15009</v>
       </c>
       <c r="H11" t="n">
         <v>704</v>
@@ -1253,7 +1253,7 @@
         <v>821</v>
       </c>
       <c r="R11" t="n">
-        <v>13013</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:52</t>
+          <t>2026-10-06 21:20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7409327</v>
+        <v>2.7260983</v>
       </c>
       <c r="G12" t="n">
-        <v>4732</v>
+        <v>4734</v>
       </c>
       <c r="H12" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2414</v>
+        <v>2434</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:53</t>
+          <t>2026-10-06 21:20:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:53</t>
+          <t>2026-10-06 21:20:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.39168</v>
+        <v>4.38354</v>
       </c>
       <c r="G14" t="n">
-        <v>13850</v>
+        <v>13867</v>
       </c>
       <c r="H14" t="n">
-        <v>5152</v>
+        <v>5155</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1306926</v>
+        <v>1309608</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1793</v>
+        <v>1818</v>
       </c>
       <c r="O14" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="P14" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q14" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R14" t="n">
-        <v>11403</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:53</t>
+          <t>2026-10-06 21:20:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-05 22:57:54</t>
+          <t>2026-10-06 21:20:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6825247</v>
+        <v>4.682278</v>
       </c>
       <c r="G16" t="n">
-        <v>46777</v>
+        <v>46780</v>
       </c>
       <c r="H16" t="n">
         <v>3024</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>601052</v>
+        <v>601056</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="O16" t="n">
         <v>429</v>
       </c>
       <c r="P16" t="n">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="Q16" t="n">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="R16" t="n">
-        <v>40805</v>
+        <v>40801</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.05</v>
+        <v>4.09901</v>
       </c>
       <c r="G2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H2" t="n">
         <v>183</v>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3920865</v>
+        <v>4.390524</v>
       </c>
       <c r="G3" t="n">
-        <v>31230</v>
+        <v>31240</v>
       </c>
       <c r="H3" t="n">
-        <v>9288</v>
+        <v>9292</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2449220</v>
+        <v>2453908</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.3</t>
+          <t>4.46.4</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4200</v>
+        <v>4215</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25780</v>
+        <v>25778</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.600517</v>
+        <v>3.6011636</v>
       </c>
       <c r="G4" t="n">
-        <v>25178</v>
+        <v>25183</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7388</v>
+        <v>7389</v>
       </c>
       <c r="O4" t="n">
         <v>893</v>
@@ -736,10 +736,10 @@
         <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="R4" t="n">
-        <v>14777</v>
+        <v>14796</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5232368</v>
+        <v>4.5284586</v>
       </c>
       <c r="G5" t="n">
-        <v>26980</v>
+        <v>26989</v>
       </c>
       <c r="H5" t="n">
-        <v>10041</v>
+        <v>10046</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2025</v>
+        <v>1995</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="Q5" t="n">
-        <v>1913</v>
+        <v>1894</v>
       </c>
       <c r="R5" t="n">
-        <v>21785</v>
+        <v>21841</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113306</v>
+        <v>113477</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 21:19:59</t>
+          <t>2026-10-07 21:42:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.186147</v>
+        <v>4.162393</v>
       </c>
       <c r="G7" t="n">
-        <v>3191</v>
+        <v>3193</v>
       </c>
       <c r="H7" t="n">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="O7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P7" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q7" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R7" t="n">
-        <v>2333</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:00</t>
+          <t>2026-10-07 21:42:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177982</v>
+        <v>4.1706424</v>
       </c>
       <c r="G8" t="n">
-        <v>6125</v>
+        <v>6126</v>
       </c>
       <c r="H8" t="n">
         <v>2271</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="O8" t="n">
         <v>168</v>
@@ -1035,7 +1035,7 @@
         <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4550</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:00</t>
+          <t>2026-10-07 21:42:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.652174</v>
+        <v>3.677686</v>
       </c>
       <c r="G9" t="n">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="H9" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="O9" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>821</v>
+        <v>828</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:00</t>
+          <t>2026-10-07 21:42:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>579</v>
       </c>
       <c r="H10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:00</t>
+          <t>2026-10-07 21:42:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.677661</v>
       </c>
       <c r="G11" t="n">
-        <v>15009</v>
+        <v>15012</v>
       </c>
       <c r="H11" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="O11" t="n">
         <v>123</v>
@@ -1250,10 +1250,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="R11" t="n">
-        <v>13015</v>
+        <v>13019</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:00</t>
+          <t>2026-10-07 21:42:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7260983</v>
+        <v>2.7157624</v>
       </c>
       <c r="G12" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="H12" t="n">
         <v>1968</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2434</v>
+        <v>2445</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1748</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:01</t>
+          <t>2026-10-07 21:42:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:01</t>
+          <t>2026-10-07 21:42:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.38354</v>
+        <v>4.382195</v>
       </c>
       <c r="G14" t="n">
-        <v>13867</v>
+        <v>13883</v>
       </c>
       <c r="H14" t="n">
-        <v>5155</v>
+        <v>5159</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="O14" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="P14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q14" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R14" t="n">
-        <v>11390</v>
+        <v>11399</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:01</t>
+          <t>2026-10-07 21:42:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.397143</v>
+        <v>3.3903134</v>
       </c>
       <c r="G15" t="n">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="O15" t="n">
         <v>134</v>
@@ -1545,7 +1545,7 @@
         <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2165</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 21:20:01</t>
+          <t>2026-10-07 21:42:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.682278</v>
+        <v>4.6818075</v>
       </c>
       <c r="G16" t="n">
         <v>46780</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>601056</v>
+        <v>604929</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>429</v>
       </c>
       <c r="P16" t="n">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="Q16" t="n">
         <v>2366</v>
       </c>
       <c r="R16" t="n">
-        <v>40801</v>
+        <v>40790</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:23</t>
+          <t>2026-10-08 21:35:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42188</v>
+        <v>42389</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:23</t>
+          <t>2026-10-08 21:35:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.390524</v>
+        <v>4.385473</v>
       </c>
       <c r="G3" t="n">
-        <v>31240</v>
+        <v>31250</v>
       </c>
       <c r="H3" t="n">
-        <v>9292</v>
+        <v>9293</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4215</v>
+        <v>4258</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25778</v>
+        <v>25754</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:23</t>
+          <t>2026-10-08 21:35:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6011636</v>
+        <v>3.6029696</v>
       </c>
       <c r="G4" t="n">
-        <v>25183</v>
+        <v>25193</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2647429</v>
+        <v>2648701</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7389</v>
+        <v>7382</v>
       </c>
       <c r="O4" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="P4" t="n">
         <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="R4" t="n">
-        <v>14796</v>
+        <v>14816</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:23</t>
+          <t>2026-10-08 21:36:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5284586</v>
+        <v>4.5234733</v>
       </c>
       <c r="G5" t="n">
-        <v>26989</v>
+        <v>26996</v>
       </c>
       <c r="H5" t="n">
-        <v>10046</v>
+        <v>10051</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>689819</v>
+        <v>691538</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1995</v>
+        <v>2029</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
@@ -813,7 +813,7 @@
         <v>1894</v>
       </c>
       <c r="R5" t="n">
-        <v>21841</v>
+        <v>21813</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:24</t>
+          <t>2026-10-08 21:36:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113477</v>
+        <v>113501</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:24</t>
+          <t>2026-10-08 21:36:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.162393</v>
+        <v>4.1525426</v>
       </c>
       <c r="G7" t="n">
-        <v>3193</v>
+        <v>3195</v>
       </c>
       <c r="H7" t="n">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>460565</v>
+        <v>461265</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="O7" t="n">
         <v>67</v>
       </c>
       <c r="P7" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q7" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>2318</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:24</t>
+          <t>2026-10-08 21:36:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>476516</v>
+        <v>479350</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:24</t>
+          <t>2026-10-08 21:36:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.677686</v>
+        <v>3.6885245</v>
       </c>
       <c r="G9" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H9" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185402</v>
+        <v>185575</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O9" t="n">
         <v>64</v>
@@ -1109,7 +1109,7 @@
         <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>828</v>
+        <v>832</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:24</t>
+          <t>2026-10-08 21:36:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8962264</v>
+        <v>3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>97510</v>
+        <v>97927</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,19 +1167,19 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:25</t>
+          <t>2026-10-08 21:36:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677661</v>
+        <v>4.6779027</v>
       </c>
       <c r="G11" t="n">
-        <v>15012</v>
+        <v>15013</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>277697</v>
+        <v>279041</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>820</v>
       </c>
       <c r="R11" t="n">
-        <v>13019</v>
+        <v>13021</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:25</t>
+          <t>2026-10-08 21:36:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7157624</v>
+        <v>2.7098446</v>
       </c>
       <c r="G12" t="n">
-        <v>4735</v>
+        <v>4734</v>
       </c>
       <c r="H12" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>361298</v>
+        <v>361764</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2445</v>
+        <v>2451</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1737</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:25</t>
+          <t>2026-10-08 21:36:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22467</v>
+        <v>22507</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:25</t>
+          <t>2026-10-08 21:36:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.382195</v>
+        <v>4.3769994</v>
       </c>
       <c r="G14" t="n">
-        <v>13883</v>
+        <v>13893</v>
       </c>
       <c r="H14" t="n">
-        <v>5159</v>
+        <v>5162</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1309608</v>
+        <v>1312222</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1821</v>
+        <v>1840</v>
       </c>
       <c r="O14" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q14" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="R14" t="n">
-        <v>11399</v>
+        <v>11384</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:25</t>
+          <t>2026-10-08 21:36:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3903134</v>
+        <v>3.4011462</v>
       </c>
       <c r="G15" t="n">
-        <v>3951</v>
+        <v>3953</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>419045</v>
+        <v>420583</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="O15" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2161</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-07 21:42:26</t>
+          <t>2026-10-08 21:36:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>46780</v>
       </c>
       <c r="H16" t="n">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 21:35:59</t>
+          <t>2026-10-09 21:22:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.09901</v>
       </c>
       <c r="G2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2" t="n">
         <v>183</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42389</v>
+        <v>42434</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 21:35:59</t>
+          <t>2026-10-09 21:22:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.385473</v>
+        <v>4.3850307</v>
       </c>
       <c r="G3" t="n">
-        <v>31250</v>
+        <v>31248</v>
       </c>
       <c r="H3" t="n">
-        <v>9293</v>
+        <v>9297</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2453908</v>
+        <v>2454962</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4258</v>
+        <v>4261</v>
       </c>
       <c r="O3" t="n">
         <v>325</v>
@@ -665,7 +665,7 @@
         <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25754</v>
+        <v>25748</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 21:35:59</t>
+          <t>2026-10-09 21:22:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6029696</v>
+        <v>3.6056883</v>
       </c>
       <c r="G4" t="n">
-        <v>25193</v>
+        <v>25194</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2648701</v>
+        <v>2649512</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7382</v>
+        <v>7377</v>
       </c>
       <c r="O4" t="n">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="Q4" t="n">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="R4" t="n">
-        <v>14816</v>
+        <v>14836</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:00</t>
+          <t>2026-10-09 21:22:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5234733</v>
+        <v>4.520963</v>
       </c>
       <c r="G5" t="n">
-        <v>26996</v>
+        <v>26998</v>
       </c>
       <c r="H5" t="n">
         <v>10051</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>691538</v>
+        <v>691963</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="Q5" t="n">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="R5" t="n">
-        <v>21813</v>
+        <v>21786</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:00</t>
+          <t>2026-10-09 21:22:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:01</t>
+          <t>2026-10-09 21:22:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.1525426</v>
       </c>
       <c r="G7" t="n">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="H7" t="n">
         <v>1182</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>461265</v>
+        <v>461470</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>2314</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:01</t>
+          <t>2026-10-09 21:22:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1706424</v>
+        <v>4.177982</v>
       </c>
       <c r="G8" t="n">
-        <v>6126</v>
+        <v>6127</v>
       </c>
       <c r="H8" t="n">
         <v>2271</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>479350</v>
+        <v>479982</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="O8" t="n">
         <v>168</v>
@@ -1035,7 +1035,7 @@
         <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4540</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:01</t>
+          <t>2026-10-09 21:22:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6885245</v>
+        <v>3.656</v>
       </c>
       <c r="G9" t="n">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="H9" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1097,19 +1097,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="O9" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P9" t="n">
         <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R9" t="n">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:01</t>
+          <t>2026-10-09 21:22:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.87</v>
+        <v>3.8811882</v>
       </c>
       <c r="G10" t="n">
         <v>580</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>97927</v>
+        <v>98011</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:02</t>
+          <t>2026-10-09 21:22:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6779027</v>
+        <v>4.6774435</v>
       </c>
       <c r="G11" t="n">
-        <v>15013</v>
+        <v>15015</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="O11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="R11" t="n">
-        <v>13021</v>
+        <v>13027</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:02</t>
+          <t>2026-10-09 21:22:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7098446</v>
+        <v>2.7157624</v>
       </c>
       <c r="G12" t="n">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="H12" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2451</v>
+        <v>2445</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1728</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:02</t>
+          <t>2026-10-09 21:22:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22507</v>
+        <v>22516</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:03</t>
+          <t>2026-10-09 21:22:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3769994</v>
+        <v>4.3766036</v>
       </c>
       <c r="G14" t="n">
-        <v>13893</v>
+        <v>13907</v>
       </c>
       <c r="H14" t="n">
-        <v>5162</v>
+        <v>5161</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1840</v>
+        <v>1847</v>
       </c>
       <c r="O14" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q14" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="R14" t="n">
-        <v>11384</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:03</t>
+          <t>2026-10-09 21:22:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4011462</v>
+        <v>3.3942857</v>
       </c>
       <c r="G15" t="n">
-        <v>3953</v>
+        <v>3955</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>420583</v>
+        <v>420900</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2174</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 21:36:03</t>
+          <t>2026-10-09 21:22:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6818075</v>
+        <v>4.6818824</v>
       </c>
       <c r="G16" t="n">
-        <v>46780</v>
+        <v>46781</v>
       </c>
       <c r="H16" t="n">
         <v>3025</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>604929</v>
+        <v>605911</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="O16" t="n">
         <v>429</v>
       </c>
       <c r="P16" t="n">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="Q16" t="n">
         <v>2366</v>
       </c>
       <c r="R16" t="n">
-        <v>40790</v>
+        <v>40792</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:08</t>
+          <t>2026-10-10 20:22:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42434</v>
+        <v>42436</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:08</t>
+          <t>2026-10-10 20:22:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3850307</v>
+        <v>4.3846984</v>
       </c>
       <c r="G3" t="n">
-        <v>31248</v>
+        <v>31251</v>
       </c>
       <c r="H3" t="n">
-        <v>9297</v>
+        <v>9298</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2454962</v>
+        <v>2454979</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4261</v>
+        <v>4264</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25748</v>
+        <v>25750</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:09</t>
+          <t>2026-10-10 20:22:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6056883</v>
+        <v>3.601421</v>
       </c>
       <c r="G4" t="n">
-        <v>25194</v>
+        <v>25197</v>
       </c>
       <c r="H4" t="n">
         <v>5624</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2649512</v>
+        <v>2649528</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7377</v>
+        <v>7405</v>
       </c>
       <c r="O4" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="Q4" t="n">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="R4" t="n">
-        <v>14836</v>
+        <v>14811</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:09</t>
+          <t>2026-10-10 20:22:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.520963</v>
+        <v>4.5192704</v>
       </c>
       <c r="G5" t="n">
-        <v>26998</v>
+        <v>27007</v>
       </c>
       <c r="H5" t="n">
         <v>10051</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>691963</v>
+        <v>691967</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2039</v>
+        <v>2058</v>
       </c>
       <c r="O5" t="n">
         <v>335</v>
       </c>
       <c r="P5" t="n">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="Q5" t="n">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="R5" t="n">
-        <v>21786</v>
+        <v>21791</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:09</t>
+          <t>2026-10-10 20:22:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:09</t>
+          <t>2026-10-10 20:22:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1525426</v>
+        <v>4.1694913</v>
       </c>
       <c r="G7" t="n">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="H7" t="n">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>461470</v>
+        <v>461473</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="O7" t="n">
         <v>67</v>
@@ -961,7 +961,7 @@
         <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>2313</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:10</t>
+          <t>2026-10-10 20:22:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>479982</v>
+        <v>479987</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:10</t>
+          <t>2026-10-10 20:22:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.656</v>
+        <v>3.6456692</v>
       </c>
       <c r="G9" t="n">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="H9" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185575</v>
+        <v>185723</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Oct 5, 2026</t>
+          <t>Oct 4, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="O9" t="n">
         <v>62</v>
@@ -1106,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R9" t="n">
         <v>825</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:10</t>
+          <t>2026-10-10 20:22:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1142,7 +1142,7 @@
         <v>3.8811882</v>
       </c>
       <c r="G10" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H10" t="n">
         <v>249</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98011</v>
+        <v>98014</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:10</t>
+          <t>2026-10-10 20:22:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6774435</v>
+        <v>4.677419</v>
       </c>
       <c r="G11" t="n">
-        <v>15015</v>
+        <v>15018</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>279041</v>
+        <v>280940</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="O11" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="R11" t="n">
-        <v>13027</v>
+        <v>13023</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:11</t>
+          <t>2026-10-10 20:22:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>361764</v>
+        <v>361876</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:11</t>
+          <t>2026-10-10 20:22:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22516</v>
+        <v>22517</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:11</t>
+          <t>2026-10-10 20:22:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3766036</v>
+        <v>4.346793</v>
       </c>
       <c r="G14" t="n">
-        <v>13907</v>
+        <v>13909</v>
       </c>
       <c r="H14" t="n">
-        <v>5161</v>
+        <v>5163</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1312222</v>
+        <v>1312228</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1847</v>
+        <v>1948</v>
       </c>
       <c r="O14" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P14" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q14" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="R14" t="n">
-        <v>11398</v>
+        <v>11287</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:11</t>
+          <t>2026-10-10 20:22:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3942857</v>
+        <v>3.389685</v>
       </c>
       <c r="G15" t="n">
-        <v>3955</v>
+        <v>3953</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>420900</v>
+        <v>420901</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:12</t>
+          <t>2026-10-10 20:22:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6818824</v>
+        <v>4.6819572</v>
       </c>
       <c r="G16" t="n">
-        <v>46781</v>
+        <v>46780</v>
       </c>
       <c r="H16" t="n">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>605911</v>
+        <v>605918</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         <v>2420</v>
       </c>
       <c r="O16" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P16" t="n">
         <v>769</v>
       </c>
       <c r="Q16" t="n">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="R16" t="n">
         <v>40792</v>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:02</t>
+          <t>2026-10-11 20:39:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:02</t>
+          <t>2026-10-11 20:39:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3846984</v>
+        <v>4.3847256</v>
       </c>
       <c r="G3" t="n">
-        <v>31251</v>
+        <v>31259</v>
       </c>
       <c r="H3" t="n">
         <v>9298</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2454979</v>
+        <v>2456024</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4264</v>
+        <v>4269</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -662,10 +662,10 @@
         <v>279</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="R3" t="n">
-        <v>25750</v>
+        <v>25766</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:03</t>
+          <t>2026-10-11 20:39:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.601421</v>
+        <v>3.602713</v>
       </c>
       <c r="G4" t="n">
-        <v>25197</v>
+        <v>25203</v>
       </c>
       <c r="H4" t="n">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7405</v>
+        <v>7407</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="Q4" t="n">
         <v>1219</v>
       </c>
       <c r="R4" t="n">
-        <v>14811</v>
+        <v>14831</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:03</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5192704</v>
+        <v>4.5180573</v>
       </c>
       <c r="G5" t="n">
-        <v>27007</v>
+        <v>27009</v>
       </c>
       <c r="H5" t="n">
-        <v>10051</v>
+        <v>10054</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>691967</v>
+        <v>692373</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="O5" t="n">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="P5" t="n">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="Q5" t="n">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="R5" t="n">
-        <v>21791</v>
+        <v>21784</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:03</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:03</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>4.1694913</v>
       </c>
       <c r="G7" t="n">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="H7" t="n">
         <v>1180</v>
@@ -961,7 +961,7 @@
         <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>2327</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:04</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.177982</v>
+        <v>4.1724772</v>
       </c>
       <c r="G8" t="n">
-        <v>6127</v>
+        <v>6126</v>
       </c>
       <c r="H8" t="n">
-        <v>2271</v>
+        <v>2275</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,11 +1005,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>479987</v>
+        <v>480659</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.29</t>
+          <t>2.1.30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1019,11 +1019,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sep 1, 2026</t>
+          <t>Oct 6, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="O8" t="n">
         <v>168</v>
@@ -1032,10 +1032,10 @@
         <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="R8" t="n">
-        <v>4552</v>
+        <v>4551</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:04</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6456692</v>
+        <v>3.5042734</v>
       </c>
       <c r="G9" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="H9" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185723</v>
+        <v>185854</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,23 +1093,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Oct 4, 2026</t>
+          <t>Oct 5, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="O9" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P9" t="n">
         <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>825</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:04</t>
+          <t>2026-10-11 20:39:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8811882</v>
+        <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H10" t="n">
         <v>249</v>
@@ -1167,19 +1167,19 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:05</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.677419</v>
+        <v>4.6734233</v>
       </c>
       <c r="G11" t="n">
-        <v>15018</v>
+        <v>15021</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="O11" t="n">
         <v>123</v>
@@ -1250,10 +1250,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="R11" t="n">
-        <v>13023</v>
+        <v>13001</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:05</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:05</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:06</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.346793</v>
+        <v>4.3436265</v>
       </c>
       <c r="G14" t="n">
         <v>13909</v>
       </c>
       <c r="H14" t="n">
-        <v>5163</v>
+        <v>5165</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1312228</v>
+        <v>1313184</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.7.2</t>
+          <t>10.7.3</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 8, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1948</v>
+        <v>1959</v>
       </c>
       <c r="O14" t="n">
         <v>242</v>
@@ -1471,7 +1471,7 @@
         <v>297</v>
       </c>
       <c r="R14" t="n">
-        <v>11287</v>
+        <v>11276</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:06</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-10 20:22:06</t>
+          <t>2026-10-11 20:39:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6819572</v>
+        <v>4.680376</v>
       </c>
       <c r="G16" t="n">
-        <v>46780</v>
+        <v>46783</v>
       </c>
       <c r="H16" t="n">
         <v>3026</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>605918</v>
+        <v>606754</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2420</v>
+        <v>2439</v>
       </c>
       <c r="O16" t="n">
         <v>428</v>
@@ -1616,10 +1616,10 @@
         <v>769</v>
       </c>
       <c r="Q16" t="n">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="R16" t="n">
-        <v>40792</v>
+        <v>40779</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:29</t>
+          <t>2026-10-12 23:18:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42436</v>
+        <v>42810</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:29</t>
+          <t>2026-10-12 23:18:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3847256</v>
+        <v>4.382818</v>
       </c>
       <c r="G3" t="n">
-        <v>31259</v>
+        <v>31263</v>
       </c>
       <c r="H3" t="n">
-        <v>9298</v>
+        <v>9299</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2456024</v>
+        <v>2458548</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4269</v>
+        <v>4280</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q3" t="n">
-        <v>615</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25766</v>
+        <v>25744</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:29</t>
+          <t>2026-10-12 23:18:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.602713</v>
+        <v>3.6001291</v>
       </c>
       <c r="G4" t="n">
-        <v>25203</v>
+        <v>25206</v>
       </c>
       <c r="H4" t="n">
-        <v>5625</v>
+        <v>5627</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2649528</v>
+        <v>2652416</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7407</v>
+        <v>7424</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -736,10 +736,10 @@
         <v>861</v>
       </c>
       <c r="Q4" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="R4" t="n">
-        <v>14831</v>
+        <v>14816</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5180573</v>
+        <v>4.5169983</v>
       </c>
       <c r="G5" t="n">
-        <v>27009</v>
+        <v>27013</v>
       </c>
       <c r="H5" t="n">
-        <v>10054</v>
+        <v>10062</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>692373</v>
+        <v>693443</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2062</v>
+        <v>2071</v>
       </c>
       <c r="O5" t="n">
         <v>346</v>
       </c>
       <c r="P5" t="n">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q5" t="n">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="R5" t="n">
-        <v>21784</v>
+        <v>21782</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>481</v>
       </c>
       <c r="H6" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113501</v>
+        <v>113646</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.0.5</t>
+          <t>4.0.9</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Oct 12, 2026</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1694913</v>
+        <v>4.088889</v>
       </c>
       <c r="G7" t="n">
-        <v>3191</v>
+        <v>3194</v>
       </c>
       <c r="H7" t="n">
         <v>1180</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>461473</v>
+        <v>462061</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="O7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P7" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="Q7" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="R7" t="n">
-        <v>2324</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="8">
@@ -972,7 +972,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1724772</v>
+        <v>4.193896</v>
       </c>
       <c r="G8" t="n">
-        <v>6126</v>
+        <v>6143</v>
       </c>
       <c r="H8" t="n">
-        <v>2275</v>
+        <v>2280</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>480659</v>
+        <v>482559</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>988</v>
+        <v>947</v>
       </c>
       <c r="O8" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="P8" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="Q8" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="R8" t="n">
-        <v>4551</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5042734</v>
+        <v>3.4830508</v>
       </c>
       <c r="G9" t="n">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H9" t="n">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1079,11 +1079,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185854</v>
+        <v>186151</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.8.2GMS</t>
+          <t>1.8.3GMS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1093,11 +1093,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Oct 5, 2026</t>
+          <t>Oct 11, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="O9" t="n">
         <v>67</v>
@@ -1109,7 +1109,7 @@
         <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:30</t>
+          <t>2026-10-12 23:18:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>280940</v>
+        <v>288153</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22517</v>
+        <v>22556</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3436265</v>
+        <v>4.3482704</v>
       </c>
       <c r="G14" t="n">
-        <v>13909</v>
+        <v>13920</v>
       </c>
       <c r="H14" t="n">
-        <v>5165</v>
+        <v>5172</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1313184</v>
+        <v>1315346</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1959</v>
+        <v>1947</v>
       </c>
       <c r="O14" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P14" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q14" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R14" t="n">
-        <v>11276</v>
+        <v>11304</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-11 20:39:31</t>
+          <t>2026-10-12 23:18:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1581,7 +1581,7 @@
         <v>46783</v>
       </c>
       <c r="H16" t="n">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>606754</v>
+        <v>609444</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:35</t>
+          <t>2026-10-13 21:36:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:36</t>
+          <t>2026-10-13 21:36:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.382818</v>
+        <v>4.384477</v>
       </c>
       <c r="G3" t="n">
-        <v>31263</v>
+        <v>31269</v>
       </c>
       <c r="H3" t="n">
-        <v>9299</v>
+        <v>9302</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4280</v>
+        <v>4269</v>
       </c>
       <c r="O3" t="n">
         <v>325</v>
@@ -665,7 +665,7 @@
         <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25744</v>
+        <v>25762</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:36</t>
+          <t>2026-10-13 21:36:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6001291</v>
+        <v>3.5975451</v>
       </c>
       <c r="G4" t="n">
-        <v>25206</v>
+        <v>25213</v>
       </c>
       <c r="H4" t="n">
         <v>5627</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2652416</v>
+        <v>2652973</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7424</v>
+        <v>7443</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
         <v>861</v>
@@ -739,7 +739,7 @@
         <v>1220</v>
       </c>
       <c r="R4" t="n">
-        <v>14816</v>
+        <v>14804</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:36</t>
+          <t>2026-10-13 21:36:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5169983</v>
+        <v>4.5161557</v>
       </c>
       <c r="G5" t="n">
-        <v>27013</v>
+        <v>27038</v>
       </c>
       <c r="H5" t="n">
-        <v>10062</v>
+        <v>10068</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>693443</v>
+        <v>693678</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>2071</v>
       </c>
       <c r="O5" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P5" t="n">
         <v>906</v>
@@ -813,7 +813,7 @@
         <v>1903</v>
       </c>
       <c r="R5" t="n">
-        <v>21782</v>
+        <v>21795</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:37</t>
+          <t>2026-10-13 21:36:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H6" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113646</v>
+        <v>113664</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.0.9</t>
+          <t>Varies with device</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -869,13 +869,9 @@
           <t>Mar 13, 2017</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Oct 12, 2026</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -887,7 +883,7 @@
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
@@ -898,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:37</t>
+          <t>2026-10-13 21:36:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -972,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:37</t>
+          <t>2026-10-13 21:36:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.193896</v>
+        <v>4.2045856</v>
       </c>
       <c r="G8" t="n">
-        <v>6143</v>
+        <v>6153</v>
       </c>
       <c r="H8" t="n">
         <v>2280</v>
@@ -1023,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="O8" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="P8" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="Q8" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R8" t="n">
-        <v>4587</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:38</t>
+          <t>2026-10-13 21:36:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1065,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4830508</v>
+        <v>3.4358974</v>
       </c>
       <c r="G9" t="n">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="H9" t="n">
         <v>562</v>
@@ -1097,19 +1093,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="O9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>777</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:38</t>
+          <t>2026-10-13 21:36:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98014</v>
+        <v>98434</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:38</t>
+          <t>2026-10-13 21:36:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6734233</v>
+        <v>4.6731634</v>
       </c>
       <c r="G11" t="n">
-        <v>15021</v>
+        <v>15023</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1223,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>288153</v>
+        <v>290060</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1237,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="O11" t="n">
         <v>123</v>
@@ -1250,10 +1246,10 @@
         <v>269</v>
       </c>
       <c r="Q11" t="n">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="R11" t="n">
-        <v>13001</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:39</t>
+          <t>2026-10-13 21:36:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1285,7 @@
         <v>4735</v>
       </c>
       <c r="H12" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>361876</v>
+        <v>362303</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:39</t>
+          <t>2026-10-13 21:36:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22556</v>
+        <v>22557</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:39</t>
+          <t>2026-10-13 21:36:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3482704</v>
+        <v>4.3520803</v>
       </c>
       <c r="G14" t="n">
-        <v>13920</v>
+        <v>13949</v>
       </c>
       <c r="H14" t="n">
-        <v>5172</v>
+        <v>5175</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,11 +1437,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1315346</v>
+        <v>1315867</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.7.3</t>
+          <t>10.7.4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1455,23 +1451,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Oct 8, 2026</t>
+          <t>Oct 12, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="O14" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="P14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q14" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="R14" t="n">
-        <v>11304</v>
+        <v>11347</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:39</t>
+          <t>2026-10-13 21:36:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1497,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.389685</v>
+        <v>3.3942857</v>
       </c>
       <c r="G15" t="n">
-        <v>3953</v>
+        <v>3955</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>420901</v>
+        <v>422262</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1529,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2163</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-12 23:18:40</t>
+          <t>2026-10-13 21:36:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.680376</v>
+        <v>4.680451</v>
       </c>
       <c r="G16" t="n">
-        <v>46783</v>
+        <v>46784</v>
       </c>
       <c r="H16" t="n">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>609444</v>
+        <v>610177</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1613,13 +1609,13 @@
         <v>428</v>
       </c>
       <c r="P16" t="n">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="Q16" t="n">
         <v>2363</v>
       </c>
       <c r="R16" t="n">
-        <v>40779</v>
+        <v>40781</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:38</t>
+          <t>2026-10-14 20:22:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42810</v>
+        <v>42834</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:39</t>
+          <t>2026-10-14 20:22:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.384477</v>
+        <v>4.3844223</v>
       </c>
       <c r="G3" t="n">
-        <v>31269</v>
+        <v>31278</v>
       </c>
       <c r="H3" t="n">
-        <v>9302</v>
+        <v>9303</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2458548</v>
+        <v>2460206</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4269</v>
+        <v>4265</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25762</v>
+        <v>25765</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:39</t>
+          <t>2026-10-14 20:22:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.5975451</v>
       </c>
       <c r="G4" t="n">
-        <v>25213</v>
+        <v>25214</v>
       </c>
       <c r="H4" t="n">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1220</v>
       </c>
       <c r="R4" t="n">
-        <v>14804</v>
+        <v>14805</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:39</t>
+          <t>2026-10-14 20:22:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -772,10 +772,10 @@
         <v>4.5161557</v>
       </c>
       <c r="G5" t="n">
-        <v>27038</v>
+        <v>27049</v>
       </c>
       <c r="H5" t="n">
-        <v>10068</v>
+        <v>10070</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>693678</v>
+        <v>694040</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2071</v>
+        <v>2061</v>
       </c>
       <c r="O5" t="n">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="P5" t="n">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q5" t="n">
-        <v>1903</v>
+        <v>1915</v>
       </c>
       <c r="R5" t="n">
-        <v>21795</v>
+        <v>21793</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:40</t>
+          <t>2026-10-14 20:22:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H6" t="n">
         <v>168</v>
@@ -871,19 +871,19 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:40</t>
+          <t>2026-10-14 20:22:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.088889</v>
       </c>
       <c r="G7" t="n">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="H7" t="n">
         <v>1180</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462061</v>
+        <v>462173</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>538</v>
       </c>
       <c r="O7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P7" t="n">
         <v>197</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:40</t>
+          <t>2026-10-14 20:22:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2045856</v>
+        <v>4.2073812</v>
       </c>
       <c r="G8" t="n">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="H8" t="n">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>482559</v>
+        <v>483945</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.30</t>
+          <t>2.1.31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oct 6, 2026</t>
+          <t>Oct 12, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="O8" t="n">
         <v>172</v>
@@ -1031,7 +1031,7 @@
         <v>226</v>
       </c>
       <c r="R8" t="n">
-        <v>4611</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:41</t>
+          <t>2026-10-14 20:22:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,10 +1064,10 @@
         <v>3.4358974</v>
       </c>
       <c r="G9" t="n">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H9" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186151</v>
+        <v>186206</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:41</t>
+          <t>2026-10-14 20:22:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:41</t>
+          <t>2026-10-14 20:22:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6731634</v>
+        <v>4.666417</v>
       </c>
       <c r="G11" t="n">
-        <v>15023</v>
+        <v>15024</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="O11" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q11" t="n">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="R11" t="n">
-        <v>12995</v>
+        <v>12967</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:42</t>
+          <t>2026-10-14 20:22:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7157624</v>
+        <v>2.7054265</v>
       </c>
       <c r="G12" t="n">
-        <v>4735</v>
+        <v>4736</v>
       </c>
       <c r="H12" t="n">
         <v>1969</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2445</v>
+        <v>2458</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1319,7 +1319,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1737</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:42</t>
+          <t>2026-10-14 20:22:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:42</t>
+          <t>2026-10-14 20:22:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3520803</v>
+        <v>4.3531203</v>
       </c>
       <c r="G14" t="n">
-        <v>13949</v>
+        <v>13965</v>
       </c>
       <c r="H14" t="n">
-        <v>5175</v>
+        <v>5177</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1315867</v>
+        <v>1317018</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10.7.4</t>
+          <t>10.7.5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1451,23 +1451,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Oct 12, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="O14" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P14" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q14" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="R14" t="n">
-        <v>11347</v>
+        <v>11360</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:42</t>
+          <t>2026-10-14 20:22:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3942857</v>
+        <v>3.3874643</v>
       </c>
       <c r="G15" t="n">
-        <v>3955</v>
+        <v>3957</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1541,7 +1541,7 @@
         <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2168</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-13 21:36:43</t>
+          <t>2026-10-14 20:22:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.680451</v>
+        <v>4.680676</v>
       </c>
       <c r="G16" t="n">
         <v>46784</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>610177</v>
+        <v>611036</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="O16" t="n">
         <v>428</v>
@@ -1612,10 +1612,10 @@
         <v>768</v>
       </c>
       <c r="Q16" t="n">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="R16" t="n">
-        <v>40781</v>
+        <v>40785</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:37</t>
+          <t>2026-10-15 20:06:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42834</v>
+        <v>42896</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:37</t>
+          <t>2026-10-15 20:06:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3844223</v>
+        <v>4.383537</v>
       </c>
       <c r="G3" t="n">
-        <v>31278</v>
+        <v>31289</v>
       </c>
       <c r="H3" t="n">
-        <v>9303</v>
+        <v>9306</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2460206</v>
+        <v>2461157</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4265</v>
+        <v>4273</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="R3" t="n">
-        <v>25765</v>
+        <v>25766</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:37</t>
+          <t>2026-10-15 20:06:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5975451</v>
+        <v>3.597285</v>
       </c>
       <c r="G4" t="n">
-        <v>25214</v>
+        <v>25217</v>
       </c>
       <c r="H4" t="n">
-        <v>5628</v>
+        <v>5627</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2652973</v>
+        <v>2653771</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7443</v>
+        <v>7448</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="P4" t="n">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="Q4" t="n">
-        <v>1220</v>
+        <v>1205</v>
       </c>
       <c r="R4" t="n">
-        <v>14805</v>
+        <v>14816</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:37</t>
+          <t>2026-10-15 20:06:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5161557</v>
+        <v>4.5167565</v>
       </c>
       <c r="G5" t="n">
-        <v>27049</v>
+        <v>27052</v>
       </c>
       <c r="H5" t="n">
-        <v>10070</v>
+        <v>10073</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>694040</v>
+        <v>694045</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="O5" t="n">
         <v>368</v>
       </c>
       <c r="P5" t="n">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q5" t="n">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="R5" t="n">
-        <v>21793</v>
+        <v>21801</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:38</t>
+          <t>2026-10-15 20:06:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113664</v>
+        <v>113685</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:38</t>
+          <t>2026-10-15 20:06:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.088889</v>
+        <v>4.075221</v>
       </c>
       <c r="G7" t="n">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="H7" t="n">
         <v>1180</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462173</v>
+        <v>462325</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="O7" t="n">
         <v>69</v>
@@ -957,7 +957,7 @@
         <v>141</v>
       </c>
       <c r="R7" t="n">
-        <v>2241</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:38</t>
+          <t>2026-10-15 20:06:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2073812</v>
+        <v>4.2038326</v>
       </c>
       <c r="G8" t="n">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="H8" t="n">
-        <v>2283</v>
+        <v>2288</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.31</t>
+          <t>2.1.32</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1015,23 +1015,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oct 12, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="O8" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P8" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="Q8" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R8" t="n">
-        <v>4618</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:38</t>
+          <t>2026-10-15 20:06:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4358974</v>
+        <v>3.4273505</v>
       </c>
       <c r="G9" t="n">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="H9" t="n">
         <v>563</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186206</v>
+        <v>186303</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="O9" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="P9" t="n">
         <v>11</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:38</t>
+          <t>2026-10-15 20:06:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98434</v>
+        <v>98531</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:39</t>
+          <t>2026-10-15 20:06:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.666417</v>
+        <v>4.657228</v>
       </c>
       <c r="G11" t="n">
-        <v>15024</v>
+        <v>15030</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>290060</v>
+        <v>293681</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="O11" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="Q11" t="n">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="R11" t="n">
-        <v>12967</v>
+        <v>12923</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:39</t>
+          <t>2026-10-15 20:06:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362303</v>
+        <v>362396</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:39</t>
+          <t>2026-10-15 20:06:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22557</v>
+        <v>22564</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:39</t>
+          <t>2026-10-15 20:06:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3531203</v>
+        <v>4.356443</v>
       </c>
       <c r="G14" t="n">
-        <v>13965</v>
+        <v>13975</v>
       </c>
       <c r="H14" t="n">
-        <v>5177</v>
+        <v>5189</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1317018</v>
+        <v>1318335</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1943</v>
+        <v>1937</v>
       </c>
       <c r="O14" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P14" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q14" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="R14" t="n">
-        <v>11360</v>
+        <v>11383</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:39</t>
+          <t>2026-10-15 20:06:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3874643</v>
+        <v>3.382857</v>
       </c>
       <c r="G15" t="n">
-        <v>3957</v>
+        <v>3959</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>422262</v>
+        <v>422544</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1541,7 +1541,7 @@
         <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 20:22:40</t>
+          <t>2026-10-15 20:06:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1574,7 +1574,7 @@
         <v>4.680676</v>
       </c>
       <c r="G16" t="n">
-        <v>46784</v>
+        <v>46783</v>
       </c>
       <c r="H16" t="n">
         <v>3028</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>611036</v>
+        <v>611920</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>2360</v>
       </c>
       <c r="R16" t="n">
-        <v>40785</v>
+        <v>40784</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:02</t>
+          <t>2026-10-16 19:45:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>426</v>
       </c>
       <c r="H2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:03</t>
+          <t>2026-10-16 19:45:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.383537</v>
+        <v>4.382437</v>
       </c>
       <c r="G3" t="n">
-        <v>31289</v>
+        <v>31297</v>
       </c>
       <c r="H3" t="n">
-        <v>9306</v>
+        <v>9307</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2461157</v>
+        <v>2462044</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Oct 1, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4273</v>
+        <v>4284</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q3" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25766</v>
+        <v>25765</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:03</t>
+          <t>2026-10-16 19:45:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.597285</v>
       </c>
       <c r="G4" t="n">
-        <v>25217</v>
+        <v>25222</v>
       </c>
       <c r="H4" t="n">
         <v>5627</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7448</v>
+        <v>7449</v>
       </c>
       <c r="O4" t="n">
         <v>879</v>
@@ -739,7 +739,7 @@
         <v>1205</v>
       </c>
       <c r="R4" t="n">
-        <v>14816</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:03</t>
+          <t>2026-10-16 19:45:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5167565</v>
+        <v>4.51657</v>
       </c>
       <c r="G5" t="n">
-        <v>27052</v>
+        <v>27060</v>
       </c>
       <c r="H5" t="n">
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="O5" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P5" t="n">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q5" t="n">
-        <v>1913</v>
+        <v>1905</v>
       </c>
       <c r="R5" t="n">
-        <v>21801</v>
+        <v>21813</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:03</t>
+          <t>2026-10-16 19:45:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113685</v>
+        <v>113686</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:04</t>
+          <t>2026-10-16 19:45:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.075221</v>
+        <v>4.071111</v>
       </c>
       <c r="G7" t="n">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="H7" t="n">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462325</v>
+        <v>462327</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="O7" t="n">
         <v>69</v>
@@ -957,7 +957,7 @@
         <v>141</v>
       </c>
       <c r="R7" t="n">
-        <v>2232</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:04</t>
+          <t>2026-10-16 19:45:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2038326</v>
+        <v>4.212727</v>
       </c>
       <c r="G8" t="n">
-        <v>6161</v>
+        <v>6175</v>
       </c>
       <c r="H8" t="n">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>483945</v>
+        <v>484668</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="O8" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="P8" t="n">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>4614</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:06</t>
+          <t>2026-10-16 19:45:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186303</v>
+        <v>186304</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:07</t>
+          <t>2026-10-16 19:45:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98531</v>
+        <v>98621</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:07</t>
+          <t>2026-10-16 19:45:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.657228</v>
+        <v>4.6562266</v>
       </c>
       <c r="G11" t="n">
-        <v>15030</v>
+        <v>15029</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1240,16 +1240,16 @@
         <v>817</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
         <v>279</v>
       </c>
       <c r="Q11" t="n">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="R11" t="n">
-        <v>12923</v>
+        <v>12910</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:07</t>
+          <t>2026-10-16 19:45:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362396</v>
+        <v>362486</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:07</t>
+          <t>2026-10-16 19:45:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:07</t>
+          <t>2026-10-16 19:45:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.356443</v>
+        <v>4.309119</v>
       </c>
       <c r="G14" t="n">
-        <v>13975</v>
+        <v>14023</v>
       </c>
       <c r="H14" t="n">
-        <v>5189</v>
+        <v>5196</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1937</v>
+        <v>2080</v>
       </c>
       <c r="O14" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="P14" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="Q14" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="R14" t="n">
-        <v>11383</v>
+        <v>11226</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:08</t>
+          <t>2026-10-16 19:45:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>422544</v>
+        <v>422547</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:08</t>
+          <t>2026-10-16 19:45:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.680676</v>
+        <v>4.680601</v>
       </c>
       <c r="G16" t="n">
         <v>46783</v>
       </c>
       <c r="H16" t="n">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>611920</v>
+        <v>612840</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="O16" t="n">
         <v>428</v>
@@ -1612,10 +1612,10 @@
         <v>768</v>
       </c>
       <c r="Q16" t="n">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="R16" t="n">
-        <v>40784</v>
+        <v>40783</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:06</t>
+          <t>2026-10-17 18:55:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.09901</v>
+        <v>4.0784316</v>
       </c>
       <c r="G2" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2" t="n">
         <v>184</v>
@@ -582,7 +582,7 @@
         <v>83</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>16</v>
@@ -591,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:06</t>
+          <t>2026-10-17 18:55:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.382437</v>
+        <v>4.3816686</v>
       </c>
       <c r="G3" t="n">
-        <v>31297</v>
+        <v>31302</v>
       </c>
       <c r="H3" t="n">
-        <v>9307</v>
+        <v>9311</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4284</v>
+        <v>4292</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -662,10 +662,10 @@
         <v>291</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="R3" t="n">
-        <v>25765</v>
+        <v>25764</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:06</t>
+          <t>2026-10-17 18:55:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.597285</v>
       </c>
       <c r="G4" t="n">
-        <v>25222</v>
+        <v>25225</v>
       </c>
       <c r="H4" t="n">
         <v>5627</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7449</v>
+        <v>7450</v>
       </c>
       <c r="O4" t="n">
         <v>879</v>
@@ -739,7 +739,7 @@
         <v>1205</v>
       </c>
       <c r="R4" t="n">
-        <v>14819</v>
+        <v>14821</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:06</t>
+          <t>2026-10-17 18:55:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.51657</v>
+        <v>4.514712</v>
       </c>
       <c r="G5" t="n">
-        <v>27060</v>
+        <v>27063</v>
       </c>
       <c r="H5" t="n">
-        <v>10074</v>
+        <v>10077</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2061</v>
+        <v>2073</v>
       </c>
       <c r="O5" t="n">
         <v>369</v>
@@ -813,7 +813,7 @@
         <v>1905</v>
       </c>
       <c r="R5" t="n">
-        <v>21813</v>
+        <v>21802</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:07</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -849,7 +849,7 @@
         <v>484</v>
       </c>
       <c r="H6" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:07</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:07</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.212727</v>
+        <v>4.230909</v>
       </c>
       <c r="G8" t="n">
-        <v>6175</v>
+        <v>6183</v>
       </c>
       <c r="H8" t="n">
-        <v>2291</v>
+        <v>2296</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="O8" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4636</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:07</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186304</v>
+        <v>186546</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:07</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:08</t>
+          <t>2026-10-17 18:55:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1219,11 +1219,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>293681</v>
+        <v>295716</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:08</t>
+          <t>2026-10-17 18:55:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,10 +1282,10 @@
         <v>2.7054265</v>
       </c>
       <c r="G12" t="n">
-        <v>4736</v>
+        <v>4737</v>
       </c>
       <c r="H12" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:08</t>
+          <t>2026-10-17 18:55:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22564</v>
+        <v>22584</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:08</t>
+          <t>2026-10-17 18:55:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.309119</v>
+        <v>4.296779</v>
       </c>
       <c r="G14" t="n">
-        <v>14023</v>
+        <v>14034</v>
       </c>
       <c r="H14" t="n">
-        <v>5196</v>
+        <v>5198</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1318335</v>
+        <v>1319367</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2080</v>
+        <v>2119</v>
       </c>
       <c r="O14" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="n">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="R14" t="n">
-        <v>11226</v>
+        <v>11181</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:08</t>
+          <t>2026-10-17 18:55:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-16 19:45:09</t>
+          <t>2026-10-17 18:55:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.680601</v>
+        <v>4.6798124</v>
       </c>
       <c r="G16" t="n">
-        <v>46783</v>
+        <v>46785</v>
       </c>
       <c r="H16" t="n">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2438</v>
+        <v>2448</v>
       </c>
       <c r="O16" t="n">
         <v>428</v>
@@ -1612,10 +1612,10 @@
         <v>768</v>
       </c>
       <c r="Q16" t="n">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="R16" t="n">
-        <v>40783</v>
+        <v>40777</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:05</t>
+          <t>2026-10-18 19:02:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>427</v>
       </c>
       <c r="H2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42896</v>
+        <v>42983</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:05</t>
+          <t>2026-10-18 19:02:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3816686</v>
+        <v>4.3776903</v>
       </c>
       <c r="G3" t="n">
-        <v>31302</v>
+        <v>31310</v>
       </c>
       <c r="H3" t="n">
-        <v>9311</v>
+        <v>9313</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4292</v>
+        <v>4322</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -662,10 +662,10 @@
         <v>291</v>
       </c>
       <c r="Q3" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="R3" t="n">
-        <v>25764</v>
+        <v>25739</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:05</t>
+          <t>2026-10-18 19:02:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.597285</v>
       </c>
       <c r="G4" t="n">
-        <v>25225</v>
+        <v>25229</v>
       </c>
       <c r="H4" t="n">
         <v>5627</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2653771</v>
+        <v>2655257</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7450</v>
+        <v>7451</v>
       </c>
       <c r="O4" t="n">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="P4" t="n">
         <v>863</v>
       </c>
       <c r="Q4" t="n">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>14821</v>
+        <v>14823</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:05</t>
+          <t>2026-10-18 19:02:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.514712</v>
+        <v>4.5155406</v>
       </c>
       <c r="G5" t="n">
-        <v>27063</v>
+        <v>27067</v>
       </c>
       <c r="H5" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,11 +783,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>694045</v>
+        <v>694760</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>406.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,23 +797,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Oct 2, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="O5" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P5" t="n">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="Q5" t="n">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="R5" t="n">
-        <v>21802</v>
+        <v>21816</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H6" t="n">
         <v>169</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113686</v>
+        <v>113808</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462327</v>
+        <v>462588</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.230909</v>
+        <v>4.2391305</v>
       </c>
       <c r="G8" t="n">
-        <v>6183</v>
+        <v>6192</v>
       </c>
       <c r="H8" t="n">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>484668</v>
+        <v>485321</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="R8" t="n">
-        <v>4687</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,10 +1138,10 @@
         <v>3.8921568</v>
       </c>
       <c r="G10" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98621</v>
+        <v>98706</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:06</t>
+          <t>2026-10-18 19:02:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6562266</v>
+        <v>4.6535025</v>
       </c>
       <c r="G11" t="n">
-        <v>15029</v>
+        <v>15030</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
         <v>279</v>
@@ -1249,7 +1249,7 @@
         <v>862</v>
       </c>
       <c r="R11" t="n">
-        <v>12910</v>
+        <v>12901</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:07</t>
+          <t>2026-10-18 19:02:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362486</v>
+        <v>362586</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:07</t>
+          <t>2026-10-18 19:02:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:07</t>
+          <t>2026-10-18 19:02:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.296779</v>
+        <v>4.2921433</v>
       </c>
       <c r="G14" t="n">
-        <v>14034</v>
+        <v>14042</v>
       </c>
       <c r="H14" t="n">
-        <v>5198</v>
+        <v>5201</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2119</v>
+        <v>2131</v>
       </c>
       <c r="O14" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P14" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="Q14" t="n">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="R14" t="n">
-        <v>11181</v>
+        <v>11159</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:07</t>
+          <t>2026-10-18 19:02:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>422547</v>
+        <v>423115</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-17 18:55:07</t>
+          <t>2026-10-18 19:02:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6798124</v>
+        <v>4.6789484</v>
       </c>
       <c r="G16" t="n">
         <v>46785</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.7</t>
+          <t>3.1.8</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Sep 9, 2026</t>
+          <t>Oct 18, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2448</v>
+        <v>2458</v>
       </c>
       <c r="O16" t="n">
         <v>428</v>
@@ -1612,10 +1612,10 @@
         <v>768</v>
       </c>
       <c r="Q16" t="n">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="R16" t="n">
-        <v>40777</v>
+        <v>40767</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:49</t>
+          <t>2026-10-19 21:17:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.0784316</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H2" t="n">
         <v>186</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>42983</v>
+        <v>43020</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -588,10 +588,10 @@
         <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:49</t>
+          <t>2026-10-19 21:17:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3776903</v>
+        <v>4.375897</v>
       </c>
       <c r="G3" t="n">
-        <v>31310</v>
+        <v>31313</v>
       </c>
       <c r="H3" t="n">
-        <v>9313</v>
+        <v>9315</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2462044</v>
+        <v>2462980</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4322</v>
+        <v>4334</v>
       </c>
       <c r="O3" t="n">
         <v>324</v>
@@ -662,10 +662,10 @@
         <v>291</v>
       </c>
       <c r="Q3" t="n">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25739</v>
+        <v>25719</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:50</t>
+          <t>2026-10-19 21:17:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,10 +698,10 @@
         <v>3.597285</v>
       </c>
       <c r="G4" t="n">
-        <v>25229</v>
+        <v>25228</v>
       </c>
       <c r="H4" t="n">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2655257</v>
+        <v>2655984</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7451</v>
+        <v>7452</v>
       </c>
       <c r="O4" t="n">
         <v>880</v>
@@ -739,7 +739,7 @@
         <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>14823</v>
+        <v>14822</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:50</t>
+          <t>2026-10-19 21:17:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5155406</v>
+        <v>4.5155277</v>
       </c>
       <c r="G5" t="n">
-        <v>27067</v>
+        <v>27074</v>
       </c>
       <c r="H5" t="n">
-        <v>10079</v>
+        <v>10082</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>694760</v>
+        <v>695103</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2075</v>
+        <v>2096</v>
       </c>
       <c r="O5" t="n">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="P5" t="n">
-        <v>897</v>
+        <v>873</v>
       </c>
       <c r="Q5" t="n">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="R5" t="n">
-        <v>21816</v>
+        <v>21838</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:50</t>
+          <t>2026-10-19 21:17:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113808</v>
+        <v>113838</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:51</t>
+          <t>2026-10-19 21:17:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462588</v>
+        <v>462709</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:52</t>
+          <t>2026-10-19 21:17:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2391305</v>
+        <v>4.225045</v>
       </c>
       <c r="G8" t="n">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="H8" t="n">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>485321</v>
+        <v>485954</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>908</v>
+        <v>933</v>
       </c>
       <c r="O8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="R8" t="n">
-        <v>4699</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:52</t>
+          <t>2026-10-19 21:17:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186546</v>
+        <v>186632</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:52</t>
+          <t>2026-10-19 21:17:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.8921568</v>
+        <v>3.9029126</v>
       </c>
       <c r="G10" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H10" t="n">
         <v>250</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98706</v>
+        <v>98800</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:52</t>
+          <t>2026-10-19 21:17:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6535025</v>
+        <v>4.6537604</v>
       </c>
       <c r="G11" t="n">
-        <v>15030</v>
+        <v>15031</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>295716</v>
+        <v>297889</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1233,23 +1233,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 14, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="O11" t="n">
         <v>155</v>
       </c>
       <c r="P11" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q11" t="n">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="R11" t="n">
-        <v>12901</v>
+        <v>12903</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:53</t>
+          <t>2026-10-19 21:17:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7054265</v>
+        <v>2.6950905</v>
       </c>
       <c r="G12" t="n">
-        <v>4737</v>
+        <v>4738</v>
       </c>
       <c r="H12" t="n">
         <v>1970</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362586</v>
+        <v>362686</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2459</v>
+        <v>2472</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1319,7 +1319,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1725</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:53</t>
+          <t>2026-10-19 21:17:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22584</v>
+        <v>22593</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:53</t>
+          <t>2026-10-19 21:17:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2921433</v>
+        <v>4.2901516</v>
       </c>
       <c r="G14" t="n">
-        <v>14042</v>
+        <v>14054</v>
       </c>
       <c r="H14" t="n">
-        <v>5201</v>
+        <v>5204</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1319367</v>
+        <v>1320390</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="O14" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="P14" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q14" t="n">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="R14" t="n">
-        <v>11159</v>
+        <v>11157</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:53</t>
+          <t>2026-10-19 21:17:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>423115</v>
+        <v>423430</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-18 19:02:54</t>
+          <t>2026-10-19 21:17:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6789484</v>
+        <v>4.6773815</v>
       </c>
       <c r="G16" t="n">
-        <v>46785</v>
+        <v>46782</v>
       </c>
       <c r="H16" t="n">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1585,11 +1585,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>612840</v>
+        <v>613764</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.8</t>
+          <t>3.1.9</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1599,23 +1599,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Oct 18, 2026</t>
+          <t>Oct 19, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2458</v>
+        <v>2479</v>
       </c>
       <c r="O16" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P16" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="Q16" t="n">
-        <v>2359</v>
+        <v>2348</v>
       </c>
       <c r="R16" t="n">
-        <v>40767</v>
+        <v>40755</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:43</t>
+          <t>2026-10-20 20:11:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>429</v>
       </c>
       <c r="H2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43020</v>
+        <v>43114</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:43</t>
+          <t>2026-10-20 20:11:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.375897</v>
+        <v>4.375673</v>
       </c>
       <c r="G3" t="n">
-        <v>31313</v>
+        <v>31322</v>
       </c>
       <c r="H3" t="n">
-        <v>9315</v>
+        <v>9317</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2462980</v>
+        <v>2465321</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4334</v>
+        <v>4337</v>
       </c>
       <c r="O3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25719</v>
+        <v>25724</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:43</t>
+          <t>2026-10-20 20:11:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.597285</v>
+        <v>3.596514</v>
       </c>
       <c r="G4" t="n">
-        <v>25228</v>
+        <v>25232</v>
       </c>
       <c r="H4" t="n">
         <v>5628</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2655984</v>
+        <v>2657514</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7452</v>
+        <v>7460</v>
       </c>
       <c r="O4" t="n">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="R4" t="n">
         <v>14822</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:44</t>
+          <t>2026-10-20 20:11:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5155277</v>
+        <v>4.5161023</v>
       </c>
       <c r="G5" t="n">
-        <v>27074</v>
+        <v>27084</v>
       </c>
       <c r="H5" t="n">
-        <v>10082</v>
+        <v>10086</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>695103</v>
+        <v>695773</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2096</v>
+        <v>2101</v>
       </c>
       <c r="O5" t="n">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="P5" t="n">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="Q5" t="n">
-        <v>1905</v>
+        <v>1911</v>
       </c>
       <c r="R5" t="n">
-        <v>21838</v>
+        <v>21850</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:44</t>
+          <t>2026-10-20 20:11:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:44</t>
+          <t>2026-10-20 20:11:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>462709</v>
+        <v>463015</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:44</t>
+          <t>2026-10-20 20:11:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.225045</v>
+        <v>4.222826</v>
       </c>
       <c r="G8" t="n">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="H8" t="n">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>485954</v>
+        <v>487713</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="O8" t="n">
         <v>157</v>
@@ -1028,10 +1028,10 @@
         <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4689</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:45</t>
+          <t>2026-10-20 20:11:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4273505</v>
+        <v>3.4957266</v>
       </c>
       <c r="G9" t="n">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="H9" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>765</v>
+        <v>789</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:45</t>
+          <t>2026-10-20 20:11:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,11 +1149,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98800</v>
+        <v>99025</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Varies with device</t>
+          <t>0.9.7</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1161,7 +1161,11 @@
           <t>May 5, 2024</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Oct 18, 2026</t>
+        </is>
+      </c>
       <c r="N10" t="n">
         <v>140</v>
       </c>
@@ -1186,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:45</t>
+          <t>2026-10-20 20:11:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6537604</v>
+        <v>4.652141</v>
       </c>
       <c r="G11" t="n">
-        <v>15031</v>
+        <v>15032</v>
       </c>
       <c r="H11" t="n">
         <v>705</v>
@@ -1219,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>297889</v>
+        <v>303146</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1233,23 +1237,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="P11" t="n">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="Q11" t="n">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="R11" t="n">
-        <v>12903</v>
+        <v>12907</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:46</t>
+          <t>2026-10-20 20:11:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1285,7 +1289,7 @@
         <v>4738</v>
       </c>
       <c r="H12" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1330,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:46</t>
+          <t>2026-10-20 20:11:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22593</v>
+        <v>22610</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:46</t>
+          <t>2026-10-20 20:11:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2901516</v>
+        <v>4.2838855</v>
       </c>
       <c r="G14" t="n">
-        <v>14054</v>
+        <v>14060</v>
       </c>
       <c r="H14" t="n">
-        <v>5204</v>
+        <v>5210</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2128</v>
+        <v>2149</v>
       </c>
       <c r="O14" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P14" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q14" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="R14" t="n">
-        <v>11157</v>
+        <v>11136</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:47</t>
+          <t>2026-10-20 20:11:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.382857</v>
+        <v>3.3817663</v>
       </c>
       <c r="G15" t="n">
-        <v>3959</v>
+        <v>3961</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1511,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>423430</v>
+        <v>424071</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="Q15" t="n">
         <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2160</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-19 21:17:47</t>
+          <t>2026-10-20 20:11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6773815</v>
+        <v>4.6741815</v>
       </c>
       <c r="G16" t="n">
-        <v>46782</v>
+        <v>46802</v>
       </c>
       <c r="H16" t="n">
-        <v>3040</v>
+        <v>3047</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1585,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>613764</v>
+        <v>616120</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1603,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2479</v>
+        <v>2509</v>
       </c>
       <c r="O16" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="P16" t="n">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="Q16" t="n">
-        <v>2348</v>
+        <v>2331</v>
       </c>
       <c r="R16" t="n">
-        <v>40755</v>
+        <v>40736</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:41</t>
+          <t>2026-10-21 20:24:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="G2" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:41</t>
+          <t>2026-10-21 20:24:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.375673</v>
+        <v>4.3755836</v>
       </c>
       <c r="G3" t="n">
-        <v>31322</v>
+        <v>31327</v>
       </c>
       <c r="H3" t="n">
-        <v>9317</v>
+        <v>9319</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2465321</v>
+        <v>2466165</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4337</v>
+        <v>4330</v>
       </c>
       <c r="O3" t="n">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="P3" t="n">
         <v>292</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:41</t>
+          <t>2026-10-21 20:24:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.596514</v>
+        <v>3.5974193</v>
       </c>
       <c r="G4" t="n">
-        <v>25232</v>
+        <v>25235</v>
       </c>
       <c r="H4" t="n">
         <v>5628</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2657514</v>
+        <v>2658863</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7460</v>
+        <v>7455</v>
       </c>
       <c r="O4" t="n">
         <v>878</v>
@@ -739,7 +739,7 @@
         <v>1204</v>
       </c>
       <c r="R4" t="n">
-        <v>14822</v>
+        <v>14830</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:41</t>
+          <t>2026-10-21 20:24:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5161023</v>
+        <v>4.5160627</v>
       </c>
       <c r="G5" t="n">
-        <v>27084</v>
+        <v>27089</v>
       </c>
       <c r="H5" t="n">
-        <v>10086</v>
+        <v>10087</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>695773</v>
+        <v>696112</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2101</v>
+        <v>2097</v>
       </c>
       <c r="O5" t="n">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="P5" t="n">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="Q5" t="n">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="R5" t="n">
-        <v>21850</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:41</t>
+          <t>2026-10-21 20:24:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113838</v>
+        <v>113898</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:42</t>
+          <t>2026-10-21 20:24:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,10 +916,10 @@
         <v>4.071111</v>
       </c>
       <c r="G7" t="n">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="H7" t="n">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="O7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P7" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q7" t="n">
         <v>141</v>
       </c>
       <c r="R7" t="n">
-        <v>2227</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:42</t>
+          <t>2026-10-21 20:24:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.222826</v>
+        <v>4.2083335</v>
       </c>
       <c r="G8" t="n">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="H8" t="n">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>487713</v>
+        <v>488300</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>932</v>
+        <v>954</v>
       </c>
       <c r="O8" t="n">
         <v>157</v>
@@ -1031,7 +1031,7 @@
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4673</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:42</t>
+          <t>2026-10-21 20:24:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4957266</v>
+        <v>3.5084746</v>
       </c>
       <c r="G9" t="n">
         <v>1340</v>
       </c>
       <c r="H9" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="O9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:43</t>
+          <t>2026-10-21 20:24:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>99025</v>
+        <v>99199</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:43</t>
+          <t>2026-10-21 20:24:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1215,7 +1215,7 @@
         <v>15032</v>
       </c>
       <c r="H11" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>303146</v>
+        <v>305355</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 14, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:43</t>
+          <t>2026-10-21 20:24:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6950905</v>
+        <v>2.6847546</v>
       </c>
       <c r="G12" t="n">
-        <v>4738</v>
+        <v>4740</v>
       </c>
       <c r="H12" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2472</v>
+        <v>2485</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1323,7 +1323,7 @@
         <v>207</v>
       </c>
       <c r="R12" t="n">
-        <v>1713</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:44</t>
+          <t>2026-10-21 20:24:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22610</v>
+        <v>22614</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:44</t>
+          <t>2026-10-21 20:24:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2838855</v>
+        <v>4.2763257</v>
       </c>
       <c r="G14" t="n">
-        <v>14060</v>
+        <v>14072</v>
       </c>
       <c r="H14" t="n">
-        <v>5210</v>
+        <v>5212</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2149</v>
+        <v>2174</v>
       </c>
       <c r="O14" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P14" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="Q14" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="R14" t="n">
-        <v>11136</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:44</t>
+          <t>2026-10-21 20:24:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3817663</v>
+        <v>3.3863637</v>
       </c>
       <c r="G15" t="n">
-        <v>3961</v>
+        <v>3962</v>
       </c>
       <c r="H15" t="n">
         <v>1599</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>424071</v>
+        <v>424358</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="O15" t="n">
         <v>123</v>
@@ -1545,7 +1545,7 @@
         <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2154</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 20:11:45</t>
+          <t>2026-10-21 20:24:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6741815</v>
+        <v>4.67645</v>
       </c>
       <c r="G16" t="n">
-        <v>46802</v>
+        <v>46813</v>
       </c>
       <c r="H16" t="n">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>616120</v>
+        <v>618017</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2509</v>
+        <v>2492</v>
       </c>
       <c r="O16" t="n">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="P16" t="n">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="Q16" t="n">
-        <v>2331</v>
+        <v>2337</v>
       </c>
       <c r="R16" t="n">
-        <v>40736</v>
+        <v>40773</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:03</t>
+          <t>2026-10-22 20:50:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.01</v>
+        <v>4.019802</v>
       </c>
       <c r="G2" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="H2" t="n">
         <v>189</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43114</v>
+        <v>43155</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -591,7 +591,7 @@
         <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:03</t>
+          <t>2026-10-22 20:50:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3755836</v>
+        <v>4.3760314</v>
       </c>
       <c r="G3" t="n">
-        <v>31327</v>
+        <v>31337</v>
       </c>
       <c r="H3" t="n">
-        <v>9319</v>
+        <v>9322</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2466165</v>
+        <v>2467104</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4330</v>
+        <v>4328</v>
       </c>
       <c r="O3" t="n">
         <v>337</v>
@@ -665,7 +665,7 @@
         <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25724</v>
+        <v>25736</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:03</t>
+          <t>2026-10-22 20:50:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5974193</v>
+        <v>3.5983236</v>
       </c>
       <c r="G4" t="n">
-        <v>25235</v>
+        <v>25239</v>
       </c>
       <c r="H4" t="n">
-        <v>5628</v>
+        <v>5627</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7455</v>
+        <v>7452</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
         <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="R4" t="n">
-        <v>14830</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:03</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5160627</v>
+        <v>4.5163155</v>
       </c>
       <c r="G5" t="n">
-        <v>27089</v>
+        <v>27098</v>
       </c>
       <c r="H5" t="n">
-        <v>10087</v>
+        <v>10091</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2097</v>
+        <v>2104</v>
       </c>
       <c r="O5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P5" t="n">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="Q5" t="n">
-        <v>1906</v>
+        <v>1891</v>
       </c>
       <c r="R5" t="n">
-        <v>21855</v>
+        <v>21881</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:04</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,10 +846,10 @@
         <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H6" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:04</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.071111</v>
+        <v>4.0657897</v>
       </c>
       <c r="G7" t="n">
-        <v>3194</v>
+        <v>3198</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463015</v>
+        <v>463167</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="O7" t="n">
         <v>70</v>
       </c>
       <c r="P7" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q7" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R7" t="n">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:04</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2083335</v>
+        <v>4.200723</v>
       </c>
       <c r="G8" t="n">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="H8" t="n">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>954</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>179</v>
@@ -1031,7 +1031,7 @@
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4652</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:04</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5084746</v>
+        <v>3.4957266</v>
       </c>
       <c r="G9" t="n">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H9" t="n">
         <v>565</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186632</v>
+        <v>186920</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="O9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:04</t>
+          <t>2026-10-22 20:50:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9.7</t>
+          <t>Varies with device</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1161,11 +1161,7 @@
           <t>May 5, 2024</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Oct 18, 2026</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>140</v>
       </c>
@@ -1179,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:05</t>
+          <t>2026-10-22 20:50:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.652141</v>
+        <v>4.6511626</v>
       </c>
       <c r="G11" t="n">
-        <v>15032</v>
+        <v>15034</v>
       </c>
       <c r="H11" t="n">
         <v>706</v>
@@ -1237,23 +1233,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="O11" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P11" t="n">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="R11" t="n">
-        <v>12907</v>
+        <v>12901</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:05</t>
+          <t>2026-10-22 20:50:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6847546</v>
+        <v>2.6881444</v>
       </c>
       <c r="G12" t="n">
         <v>4740</v>
       </c>
       <c r="H12" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1297,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362686</v>
+        <v>362910</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,19 +1307,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2485</v>
+        <v>2479</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="R12" t="n">
-        <v>1701</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:05</t>
+          <t>2026-10-22 20:50:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:05</t>
+          <t>2026-10-22 20:50:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2763257</v>
+        <v>4.2786403</v>
       </c>
       <c r="G14" t="n">
-        <v>14072</v>
+        <v>14085</v>
       </c>
       <c r="H14" t="n">
-        <v>5212</v>
+        <v>5216</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1320390</v>
+        <v>1323074</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2174</v>
+        <v>2164</v>
       </c>
       <c r="O14" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P14" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q14" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="R14" t="n">
-        <v>11118</v>
+        <v>11138</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:06</t>
+          <t>2026-10-22 20:50:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1503,7 @@
         <v>3962</v>
       </c>
       <c r="H15" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>424358</v>
+        <v>424646</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-21 20:24:06</t>
+          <t>2026-10-22 20:50:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.67645</v>
+        <v>4.6741443</v>
       </c>
       <c r="G16" t="n">
-        <v>46813</v>
+        <v>46822</v>
       </c>
       <c r="H16" t="n">
-        <v>3045</v>
+        <v>3047</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2492</v>
+        <v>2520</v>
       </c>
       <c r="O16" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P16" t="n">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="Q16" t="n">
-        <v>2337</v>
+        <v>2343</v>
       </c>
       <c r="R16" t="n">
-        <v>40773</v>
+        <v>40751</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:40</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43155</v>
+        <v>43186</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:40</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3760314</v>
+        <v>4.3728933</v>
       </c>
       <c r="G3" t="n">
-        <v>31337</v>
+        <v>31344</v>
       </c>
       <c r="H3" t="n">
-        <v>9322</v>
+        <v>9323</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2467104</v>
+        <v>2469022</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.4</t>
+          <t>4.46.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4328</v>
+        <v>4348</v>
       </c>
       <c r="O3" t="n">
         <v>337</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
         <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25736</v>
+        <v>25713</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:40</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5983236</v>
+        <v>3.5992267</v>
       </c>
       <c r="G4" t="n">
-        <v>25239</v>
+        <v>25244</v>
       </c>
       <c r="H4" t="n">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2658863</v>
+        <v>2659551</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7452</v>
+        <v>7448</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="Q4" t="n">
         <v>1203</v>
       </c>
       <c r="R4" t="n">
-        <v>14839</v>
+        <v>14849</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5163155</v>
+        <v>4.5173554</v>
       </c>
       <c r="G5" t="n">
-        <v>27098</v>
+        <v>27113</v>
       </c>
       <c r="H5" t="n">
-        <v>10091</v>
+        <v>10094</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>696112</v>
+        <v>696467</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2104</v>
+        <v>2093</v>
       </c>
       <c r="O5" t="n">
         <v>357</v>
       </c>
       <c r="P5" t="n">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="Q5" t="n">
-        <v>1891</v>
+        <v>1882</v>
       </c>
       <c r="R5" t="n">
-        <v>21881</v>
+        <v>21902</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="G6" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H6" t="n">
         <v>170</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113898</v>
+        <v>113965</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.0657897</v>
+        <v>4.069869</v>
       </c>
       <c r="G7" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463167</v>
+        <v>463317</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="O7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P7" t="n">
         <v>195</v>
       </c>
       <c r="Q7" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R7" t="n">
-        <v>2229</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.200723</v>
+        <v>4.19349</v>
       </c>
       <c r="G8" t="n">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="H8" t="n">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>488300</v>
+        <v>488895</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="O8" t="n">
         <v>145</v>
@@ -1031,7 +1031,7 @@
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4648</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186920</v>
+        <v>186985</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:41</t>
+          <t>2026-10-23 20:08:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:42</t>
+          <t>2026-10-23 20:08:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1208,7 +1208,7 @@
         <v>4.6511626</v>
       </c>
       <c r="G11" t="n">
-        <v>15034</v>
+        <v>15035</v>
       </c>
       <c r="H11" t="n">
         <v>706</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>305355</v>
+        <v>307164</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 14, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1249,7 +1249,7 @@
         <v>845</v>
       </c>
       <c r="R11" t="n">
-        <v>12901</v>
+        <v>12902</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:42</t>
+          <t>2026-10-23 20:08:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362910</v>
+        <v>363114</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:42</t>
+          <t>2026-10-23 20:08:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22614</v>
+        <v>22623</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:42</t>
+          <t>2026-10-23 20:08:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2786403</v>
+        <v>4.272064</v>
       </c>
       <c r="G14" t="n">
-        <v>14085</v>
+        <v>14104</v>
       </c>
       <c r="H14" t="n">
         <v>5216</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1323074</v>
+        <v>1323747</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2164</v>
+        <v>2180</v>
       </c>
       <c r="O14" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="P14" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q14" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="R14" t="n">
-        <v>11138</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:43</t>
+          <t>2026-10-23 20:08:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3863637</v>
+        <v>3.3885715</v>
       </c>
       <c r="G15" t="n">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="H15" t="n">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>424646</v>
+        <v>424906</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,19 +1529,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2160</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-22 20:50:43</t>
+          <t>2026-10-23 20:08:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6741443</v>
+        <v>4.6709905</v>
       </c>
       <c r="G16" t="n">
-        <v>46822</v>
+        <v>46827</v>
       </c>
       <c r="H16" t="n">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2520</v>
+        <v>2550</v>
       </c>
       <c r="O16" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="P16" t="n">
         <v>784</v>
       </c>
       <c r="Q16" t="n">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="R16" t="n">
-        <v>40751</v>
+        <v>40719</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,10 +550,10 @@
         <v>4.019802</v>
       </c>
       <c r="G2" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3728933</v>
+        <v>4.373567</v>
       </c>
       <c r="G3" t="n">
-        <v>31344</v>
+        <v>31347</v>
       </c>
       <c r="H3" t="n">
-        <v>9323</v>
+        <v>9327</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4348</v>
+        <v>4343</v>
       </c>
       <c r="O3" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25713</v>
+        <v>25720</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5992267</v>
+        <v>3.6003861</v>
       </c>
       <c r="G4" t="n">
-        <v>25244</v>
+        <v>25249</v>
       </c>
       <c r="H4" t="n">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7448</v>
+        <v>7440</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
@@ -736,10 +736,10 @@
         <v>860</v>
       </c>
       <c r="Q4" t="n">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="R4" t="n">
-        <v>14849</v>
+        <v>14850</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5173554</v>
+        <v>4.5159025</v>
       </c>
       <c r="G5" t="n">
-        <v>27113</v>
+        <v>27120</v>
       </c>
       <c r="H5" t="n">
-        <v>10094</v>
+        <v>10095</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2093</v>
+        <v>2105</v>
       </c>
       <c r="O5" t="n">
         <v>357</v>
@@ -810,10 +810,10 @@
         <v>873</v>
       </c>
       <c r="Q5" t="n">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="R5" t="n">
-        <v>21902</v>
+        <v>21899</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:39</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:40</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.19349</v>
       </c>
       <c r="G8" t="n">
-        <v>6212</v>
+        <v>6213</v>
       </c>
       <c r="H8" t="n">
         <v>2305</v>
@@ -1031,7 +1031,7 @@
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4639</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:40</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:40</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <v>582</v>
       </c>
       <c r="H10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:40</t>
+          <t>2026-10-24 19:07:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1208,7 +1208,7 @@
         <v>4.6511626</v>
       </c>
       <c r="G11" t="n">
-        <v>15035</v>
+        <v>15034</v>
       </c>
       <c r="H11" t="n">
         <v>706</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1249,7 +1249,7 @@
         <v>845</v>
       </c>
       <c r="R11" t="n">
-        <v>12902</v>
+        <v>12901</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:41</t>
+          <t>2026-10-24 19:07:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:41</t>
+          <t>2026-10-24 19:07:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:41</t>
+          <t>2026-10-24 19:07:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.272064</v>
+        <v>4.269679</v>
       </c>
       <c r="G14" t="n">
         <v>14104</v>
       </c>
       <c r="H14" t="n">
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2180</v>
+        <v>2188</v>
       </c>
       <c r="O14" t="n">
         <v>287</v>
@@ -1467,7 +1467,7 @@
         <v>328</v>
       </c>
       <c r="R14" t="n">
-        <v>11130</v>
+        <v>11122</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:41</t>
+          <t>2026-10-24 19:07:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-23 20:08:42</t>
+          <t>2026-10-24 19:07:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6709905</v>
+        <v>4.670071</v>
       </c>
       <c r="G16" t="n">
-        <v>46827</v>
+        <v>46829</v>
       </c>
       <c r="H16" t="n">
         <v>3048</v>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2550</v>
+        <v>2569</v>
       </c>
       <c r="O16" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="P16" t="n">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="Q16" t="n">
-        <v>2341</v>
+        <v>2313</v>
       </c>
       <c r="R16" t="n">
-        <v>40719</v>
+        <v>40733</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:23</t>
+          <t>2026-10-25 19:31:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.019802</v>
+        <v>4.04</v>
       </c>
       <c r="G2" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H2" t="n">
         <v>190</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43186</v>
+        <v>43276</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -588,7 +588,7 @@
         <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
         <v>303</v>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:23</t>
+          <t>2026-10-25 19:31:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.373567</v>
+        <v>4.3731184</v>
       </c>
       <c r="G3" t="n">
-        <v>31347</v>
+        <v>31353</v>
       </c>
       <c r="H3" t="n">
-        <v>9327</v>
+        <v>9330</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2469022</v>
+        <v>2470588</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4343</v>
+        <v>4348</v>
       </c>
       <c r="O3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25720</v>
+        <v>25722</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:23</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6003861</v>
+        <v>3.6006432</v>
       </c>
       <c r="G4" t="n">
-        <v>25249</v>
+        <v>25246</v>
       </c>
       <c r="H4" t="n">
         <v>5629</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2659551</v>
+        <v>2660268</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7440</v>
+        <v>7434</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="Q4" t="n">
-        <v>1218</v>
+        <v>1232</v>
       </c>
       <c r="R4" t="n">
-        <v>14850</v>
+        <v>14837</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:23</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5159025</v>
+        <v>4.514061</v>
       </c>
       <c r="G5" t="n">
-        <v>27120</v>
+        <v>27124</v>
       </c>
       <c r="H5" t="n">
-        <v>10095</v>
+        <v>10097</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>696467</v>
+        <v>697246</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2105</v>
+        <v>2119</v>
       </c>
       <c r="O5" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P5" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q5" t="n">
-        <v>1880</v>
+        <v>1873</v>
       </c>
       <c r="R5" t="n">
-        <v>21899</v>
+        <v>21896</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>113965</v>
+        <v>114064</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463317</v>
+        <v>463628</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.19349</v>
+        <v>4.200723</v>
       </c>
       <c r="G8" t="n">
         <v>6213</v>
       </c>
       <c r="H8" t="n">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>488895</v>
+        <v>490155</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
         <v>145</v>
@@ -1031,7 +1031,7 @@
         <v>258</v>
       </c>
       <c r="R8" t="n">
-        <v>4638</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4957266</v>
+        <v>3.4745762</v>
       </c>
       <c r="G9" t="n">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H9" t="n">
         <v>565</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>186985</v>
+        <v>187189</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9029126</v>
+        <v>3.875</v>
       </c>
       <c r="G10" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H10" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>99199</v>
+        <v>99374</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:24</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1208,10 +1208,10 @@
         <v>4.6511626</v>
       </c>
       <c r="G11" t="n">
-        <v>15034</v>
+        <v>15035</v>
       </c>
       <c r="H11" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>307164</v>
+        <v>310796</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>845</v>
       </c>
       <c r="R11" t="n">
-        <v>12901</v>
+        <v>12902</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:25</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>363114</v>
+        <v>363368</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:25</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22623</v>
+        <v>22646</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:25</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.269679</v>
+        <v>4.2707424</v>
       </c>
       <c r="G14" t="n">
-        <v>14104</v>
+        <v>14106</v>
       </c>
       <c r="H14" t="n">
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1323747</v>
+        <v>1325545</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="O14" t="n">
         <v>287</v>
@@ -1467,7 +1467,7 @@
         <v>328</v>
       </c>
       <c r="R14" t="n">
-        <v>11122</v>
+        <v>11127</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:25</t>
+          <t>2026-10-25 19:31:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>424906</v>
+        <v>425216</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-24 19:07:25</t>
+          <t>2026-10-25 19:31:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.670071</v>
+        <v>4.67015</v>
       </c>
       <c r="G16" t="n">
-        <v>46829</v>
+        <v>46831</v>
       </c>
       <c r="H16" t="n">
         <v>3048</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>618017</v>
+        <v>620095</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="O16" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P16" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Q16" t="n">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="R16" t="n">
-        <v>40733</v>
+        <v>40736</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:24</t>
+          <t>2026-10-26 21:15:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43276</v>
+        <v>43359</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:24</t>
+          <t>2026-10-26 21:15:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3731184</v>
+        <v>4.3728933</v>
       </c>
       <c r="G3" t="n">
-        <v>31353</v>
+        <v>31356</v>
       </c>
       <c r="H3" t="n">
         <v>9330</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4348</v>
+        <v>4350</v>
       </c>
       <c r="O3" t="n">
         <v>337</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6006432</v>
+        <v>3.5943153</v>
       </c>
       <c r="G4" t="n">
-        <v>25246</v>
+        <v>25249</v>
       </c>
       <c r="H4" t="n">
         <v>5629</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2660268</v>
+        <v>2661445</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7434</v>
+        <v>7470</v>
       </c>
       <c r="O4" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="P4" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="Q4" t="n">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="R4" t="n">
-        <v>14837</v>
+        <v>14793</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.514061</v>
+        <v>4.5142384</v>
       </c>
       <c r="G5" t="n">
-        <v>27124</v>
+        <v>27130</v>
       </c>
       <c r="H5" t="n">
         <v>10097</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>697246</v>
+        <v>697909</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2119</v>
+        <v>2115</v>
       </c>
       <c r="O5" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P5" t="n">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="Q5" t="n">
-        <v>1873</v>
+        <v>1891</v>
       </c>
       <c r="R5" t="n">
-        <v>21896</v>
+        <v>21889</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="G6" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H6" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>114064</v>
+        <v>114136</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>28</v>
       </c>
       <c r="R6" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.069869</v>
+        <v>4.056522</v>
       </c>
       <c r="G7" t="n">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463628</v>
+        <v>463897</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="O7" t="n">
         <v>68</v>
       </c>
       <c r="P7" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Q7" t="n">
         <v>138</v>
       </c>
       <c r="R7" t="n">
-        <v>2234</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.200723</v>
+        <v>4.198915</v>
       </c>
       <c r="G8" t="n">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="H8" t="n">
         <v>2308</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>490155</v>
+        <v>491282</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O8" t="n">
         <v>145</v>
@@ -1028,10 +1028,10 @@
         <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="R8" t="n">
-        <v>4650</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:25</t>
+          <t>2026-10-26 21:15:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4745762</v>
+        <v>3.440678</v>
       </c>
       <c r="G9" t="n">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="H9" t="n">
         <v>565</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>187189</v>
+        <v>187353</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>784</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.875</v>
+        <v>3.847619</v>
       </c>
       <c r="G10" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>99374</v>
+        <v>99589</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6511626</v>
+        <v>4.651685</v>
       </c>
       <c r="G11" t="n">
-        <v>15035</v>
+        <v>15037</v>
       </c>
       <c r="H11" t="n">
         <v>707</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>310796</v>
+        <v>315000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1233,11 +1233,11 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Oct 14, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O11" t="n">
         <v>179</v>
@@ -1246,10 +1246,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="R11" t="n">
-        <v>12902</v>
+        <v>12907</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6881444</v>
+        <v>2.6925066</v>
       </c>
       <c r="G12" t="n">
-        <v>4740</v>
+        <v>4741</v>
       </c>
       <c r="H12" t="n">
         <v>1971</v>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>363368</v>
+        <v>363620</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2479</v>
+        <v>2474</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q12" t="n">
         <v>219</v>
       </c>
       <c r="R12" t="n">
-        <v>1697</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22646</v>
+        <v>22668</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2707424</v>
+        <v>4.275488</v>
       </c>
       <c r="G14" t="n">
-        <v>14106</v>
+        <v>14115</v>
       </c>
       <c r="H14" t="n">
-        <v>5218</v>
+        <v>5219</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1325545</v>
+        <v>1327239</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2186</v>
+        <v>2173</v>
       </c>
       <c r="O14" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P14" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q14" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="R14" t="n">
-        <v>11127</v>
+        <v>11154</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:26</t>
+          <t>2026-10-26 21:15:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1500,10 +1500,10 @@
         <v>3.3885715</v>
       </c>
       <c r="G15" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="H15" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>425216</v>
+        <v>425676</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 19:31:27</t>
+          <t>2026-10-26 21:15:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>620095</v>
+        <v>621904</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:08</t>
+          <t>2026-10-27 21:02:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:09</t>
+          <t>2026-10-27 21:02:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3728933</v>
+        <v>4.374687</v>
       </c>
       <c r="G3" t="n">
-        <v>31356</v>
+        <v>31367</v>
       </c>
       <c r="H3" t="n">
-        <v>9330</v>
+        <v>9332</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2470588</v>
+        <v>2470589</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Oct 23, 2026</t>
+          <t>Oct 25, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4350</v>
+        <v>4339</v>
       </c>
       <c r="O3" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25722</v>
+        <v>25747</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:09</t>
+          <t>2026-10-27 21:02:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5943153</v>
+        <v>3.594577</v>
       </c>
       <c r="G4" t="n">
         <v>25249</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2661445</v>
+        <v>2661452</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7470</v>
+        <v>7464</v>
       </c>
       <c r="O4" t="n">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="P4" t="n">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1239</v>
+        <v>1253</v>
       </c>
       <c r="R4" t="n">
-        <v>14793</v>
+        <v>14782</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:09</t>
+          <t>2026-10-27 21:02:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5142384</v>
+        <v>4.514439</v>
       </c>
       <c r="G5" t="n">
         <v>27130</v>
       </c>
       <c r="H5" t="n">
-        <v>10097</v>
+        <v>10098</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>872</v>
       </c>
       <c r="Q5" t="n">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="R5" t="n">
-        <v>21889</v>
+        <v>21891</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:09</t>
+          <t>2026-10-27 21:02:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:10</t>
+          <t>2026-10-27 21:02:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.056522</v>
+        <v>4.060606</v>
       </c>
       <c r="G7" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="O7" t="n">
         <v>68</v>
@@ -954,10 +954,10 @@
         <v>193</v>
       </c>
       <c r="Q7" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R7" t="n">
-        <v>2224</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:10</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:10</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.440678</v>
+        <v>3.4067798</v>
       </c>
       <c r="G9" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H9" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="O9" t="n">
         <v>56</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>773</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:10</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.847619</v>
+        <v>3.8317757</v>
       </c>
       <c r="G10" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H10" t="n">
         <v>254</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="R10" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:10</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.651685</v>
+        <v>4.6514244</v>
       </c>
       <c r="G11" t="n">
-        <v>15037</v>
+        <v>15036</v>
       </c>
       <c r="H11" t="n">
         <v>707</v>
@@ -1249,7 +1249,7 @@
         <v>844</v>
       </c>
       <c r="R11" t="n">
-        <v>12907</v>
+        <v>12904</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:11</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6925066</v>
+        <v>2.6881444</v>
       </c>
       <c r="G12" t="n">
-        <v>4741</v>
+        <v>4742</v>
       </c>
       <c r="H12" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2474</v>
+        <v>2480</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="n">
         <v>219</v>
       </c>
       <c r="R12" t="n">
-        <v>1702</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:11</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:11</t>
+          <t>2026-10-27 21:02:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.275488</v>
+        <v>4.2754145</v>
       </c>
       <c r="G14" t="n">
-        <v>14115</v>
+        <v>14118</v>
       </c>
       <c r="H14" t="n">
-        <v>5219</v>
+        <v>5220</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2173</v>
+        <v>2167</v>
       </c>
       <c r="O14" t="n">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="P14" t="n">
         <v>172</v>
       </c>
       <c r="Q14" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R14" t="n">
-        <v>11154</v>
+        <v>11155</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:11</t>
+          <t>2026-10-27 21:02:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3885715</v>
+        <v>3.377143</v>
       </c>
       <c r="G15" t="n">
         <v>3964</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1525,11 +1525,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 22, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1404</v>
+        <v>1415</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1541,7 +1541,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2163</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-26 21:15:11</t>
+          <t>2026-10-27 21:02:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.67015</v>
+        <v>4.6695137</v>
       </c>
       <c r="G16" t="n">
-        <v>46831</v>
+        <v>46833</v>
       </c>
       <c r="H16" t="n">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2567</v>
+        <v>2576</v>
       </c>
       <c r="O16" t="n">
         <v>432</v>
@@ -1612,10 +1612,10 @@
         <v>777</v>
       </c>
       <c r="Q16" t="n">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="R16" t="n">
-        <v>40736</v>
+        <v>40732</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:15</t>
+          <t>2026-10-28 21:23:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43359</v>
+        <v>43360</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:16</t>
+          <t>2026-10-28 21:23:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.374687</v>
+        <v>4.373033</v>
       </c>
       <c r="G3" t="n">
-        <v>31367</v>
+        <v>31378</v>
       </c>
       <c r="H3" t="n">
-        <v>9332</v>
+        <v>9334</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4339</v>
+        <v>4354</v>
       </c>
       <c r="O3" t="n">
         <v>335</v>
@@ -662,10 +662,10 @@
         <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>25747</v>
+        <v>25744</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:16</t>
+          <t>2026-10-28 21:23:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.594577</v>
+        <v>3.5972939</v>
       </c>
       <c r="G4" t="n">
-        <v>25249</v>
+        <v>25253</v>
       </c>
       <c r="H4" t="n">
         <v>5629</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7464</v>
+        <v>7451</v>
       </c>
       <c r="O4" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P4" t="n">
         <v>862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="R4" t="n">
-        <v>14782</v>
+        <v>14805</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:16</t>
+          <t>2026-10-28 21:23:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.514439</v>
+        <v>4.5155025</v>
       </c>
       <c r="G5" t="n">
-        <v>27130</v>
+        <v>27138</v>
       </c>
       <c r="H5" t="n">
-        <v>10098</v>
+        <v>10099</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>697909</v>
+        <v>697911</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2115</v>
+        <v>2108</v>
       </c>
       <c r="O5" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P5" t="n">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="Q5" t="n">
-        <v>1890</v>
+        <v>1906</v>
       </c>
       <c r="R5" t="n">
-        <v>21891</v>
+        <v>21898</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:16</t>
+          <t>2026-10-28 21:23:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:16</t>
+          <t>2026-10-28 21:23:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.060606</v>
       </c>
       <c r="G7" t="n">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463897</v>
+        <v>463899</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O7" t="n">
         <v>68</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.198915</v>
       </c>
       <c r="G8" t="n">
-        <v>6217</v>
+        <v>6219</v>
       </c>
       <c r="H8" t="n">
         <v>2308</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>491282</v>
+        <v>491284</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>269</v>
       </c>
       <c r="R8" t="n">
-        <v>4641</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4067798</v>
+        <v>3.4322033</v>
       </c>
       <c r="G9" t="n">
         <v>1345</v>
       </c>
       <c r="H9" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>477</v>
       </c>
       <c r="O9" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="P9" t="n">
         <v>11</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>763</v>
+        <v>774</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1208,10 +1208,10 @@
         <v>4.6514244</v>
       </c>
       <c r="G11" t="n">
-        <v>15036</v>
+        <v>15034</v>
       </c>
       <c r="H11" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>315000</v>
+        <v>315007</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>844</v>
       </c>
       <c r="R11" t="n">
-        <v>12904</v>
+        <v>12903</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6881444</v>
+        <v>2.7028425</v>
       </c>
       <c r="G12" t="n">
-        <v>4742</v>
+        <v>4744</v>
       </c>
       <c r="H12" t="n">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2480</v>
+        <v>2463</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
       </c>
       <c r="P12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q12" t="n">
         <v>219</v>
       </c>
       <c r="R12" t="n">
-        <v>1697</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:18</t>
+          <t>2026-10-28 21:23:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2754145</v>
+        <v>4.217459</v>
       </c>
       <c r="G14" t="n">
-        <v>14118</v>
+        <v>14127</v>
       </c>
       <c r="H14" t="n">
-        <v>5220</v>
+        <v>5221</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1327239</v>
+        <v>1327243</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2167</v>
+        <v>2344</v>
       </c>
       <c r="O14" t="n">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="P14" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="Q14" t="n">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="R14" t="n">
-        <v>11155</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:19</t>
+          <t>2026-10-28 21:23:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1500,10 +1500,10 @@
         <v>3.377143</v>
       </c>
       <c r="G15" t="n">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="H15" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 21:02:19</t>
+          <t>2026-10-28 21:23:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6695137</v>
+        <v>4.669512</v>
       </c>
       <c r="G16" t="n">
-        <v>46833</v>
+        <v>46832</v>
       </c>
       <c r="H16" t="n">
-        <v>3049</v>
+        <v>3051</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="O16" t="n">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="P16" t="n">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="Q16" t="n">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="R16" t="n">
-        <v>40732</v>
+        <v>40736</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:55</t>
+          <t>2026-10-29 21:29:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:55</t>
+          <t>2026-10-29 21:29:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.373033</v>
+        <v>4.3715205</v>
       </c>
       <c r="G3" t="n">
-        <v>31378</v>
+        <v>31384</v>
       </c>
       <c r="H3" t="n">
-        <v>9334</v>
+        <v>9336</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -649,11 +649,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Oct 25, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4354</v>
+        <v>4367</v>
       </c>
       <c r="O3" t="n">
         <v>335</v>
@@ -662,10 +662,10 @@
         <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R3" t="n">
-        <v>25744</v>
+        <v>25738</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:55</t>
+          <t>2026-10-29 21:29:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5972939</v>
+        <v>3.598197</v>
       </c>
       <c r="G4" t="n">
-        <v>25253</v>
+        <v>25262</v>
       </c>
       <c r="H4" t="n">
-        <v>5629</v>
+        <v>5631</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7451</v>
+        <v>7448</v>
       </c>
       <c r="O4" t="n">
         <v>877</v>
       </c>
       <c r="P4" t="n">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="Q4" t="n">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="R4" t="n">
-        <v>14805</v>
+        <v>14817</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:55</t>
+          <t>2026-10-29 21:29:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5155025</v>
+        <v>4.5160756</v>
       </c>
       <c r="G5" t="n">
-        <v>27138</v>
+        <v>27144</v>
       </c>
       <c r="H5" t="n">
-        <v>10099</v>
+        <v>10104</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2108</v>
+        <v>2113</v>
       </c>
       <c r="O5" t="n">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="P5" t="n">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="Q5" t="n">
-        <v>1906</v>
+        <v>1913</v>
       </c>
       <c r="R5" t="n">
-        <v>21898</v>
+        <v>21906</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:56</t>
+          <t>2026-10-29 21:29:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:56</t>
+          <t>2026-10-29 21:29:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.060606</v>
+        <v>4.0646553</v>
       </c>
       <c r="G7" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="H7" t="n">
         <v>1181</v>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="O7" t="n">
         <v>68</v>
       </c>
       <c r="P7" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q7" t="n">
         <v>137</v>
       </c>
       <c r="R7" t="n">
-        <v>2230</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:56</t>
+          <t>2026-10-29 21:29:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.198915</v>
+        <v>4.201802</v>
       </c>
       <c r="G8" t="n">
-        <v>6219</v>
+        <v>6222</v>
       </c>
       <c r="H8" t="n">
         <v>2308</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R8" t="n">
-        <v>4643</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:56</t>
+          <t>2026-10-29 21:29:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,10 +1064,10 @@
         <v>3.4322033</v>
       </c>
       <c r="G9" t="n">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H9" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O9" t="n">
         <v>45</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:56</t>
+          <t>2026-10-29 21:29:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:57</t>
+          <t>2026-10-29 21:29:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6514244</v>
+        <v>4.651913</v>
       </c>
       <c r="G11" t="n">
-        <v>15034</v>
+        <v>15038</v>
       </c>
       <c r="H11" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="O11" t="n">
         <v>179</v>
@@ -1246,10 +1246,10 @@
         <v>281</v>
       </c>
       <c r="Q11" t="n">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="R11" t="n">
-        <v>12903</v>
+        <v>12916</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:57</t>
+          <t>2026-10-29 21:29:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7028425</v>
+        <v>2.6925066</v>
       </c>
       <c r="G12" t="n">
-        <v>4744</v>
+        <v>4746</v>
       </c>
       <c r="H12" t="n">
         <v>1974</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2463</v>
+        <v>2476</v>
       </c>
       <c r="O12" t="n">
         <v>134</v>
@@ -1319,7 +1319,7 @@
         <v>219</v>
       </c>
       <c r="R12" t="n">
-        <v>1715</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="13">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:57</t>
+          <t>2026-10-29 21:29:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:57</t>
+          <t>2026-10-29 21:29:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.217459</v>
+        <v>4.216783</v>
       </c>
       <c r="G14" t="n">
-        <v>14127</v>
+        <v>14131</v>
       </c>
       <c r="H14" t="n">
-        <v>5221</v>
+        <v>5225</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2344</v>
+        <v>2349</v>
       </c>
       <c r="O14" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P14" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q14" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R14" t="n">
-        <v>10933</v>
+        <v>10935</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:57</t>
+          <t>2026-10-29 21:29:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.377143</v>
+        <v>3.3760684</v>
       </c>
       <c r="G15" t="n">
-        <v>3965</v>
+        <v>3967</v>
       </c>
       <c r="H15" t="n">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1529,19 +1529,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="Q15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R15" t="n">
-        <v>2152</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-28 21:23:58</t>
+          <t>2026-10-29 21:29:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.669512</v>
+        <v>4.669114</v>
       </c>
       <c r="G16" t="n">
-        <v>46832</v>
+        <v>46838</v>
       </c>
       <c r="H16" t="n">
-        <v>3051</v>
+        <v>3053</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="O16" t="n">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="P16" t="n">
         <v>765</v>
       </c>
       <c r="Q16" t="n">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="R16" t="n">
-        <v>40736</v>
+        <v>40735</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:08</t>
+          <t>2026-10-30 21:10:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="G2" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H2" t="n">
         <v>190</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43360</v>
+        <v>43482</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
         <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:09</t>
+          <t>2026-10-30 21:10:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3715205</v>
+        <v>4.3678365</v>
       </c>
       <c r="G3" t="n">
-        <v>31384</v>
+        <v>31387</v>
       </c>
       <c r="H3" t="n">
         <v>9336</v>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2470589</v>
+        <v>2472947</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.46.5</t>
+          <t>4.46.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4367</v>
+        <v>4395</v>
       </c>
       <c r="O3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="R3" t="n">
-        <v>25738</v>
+        <v>25709</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:09</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.598197</v>
+        <v>3.598329</v>
       </c>
       <c r="G4" t="n">
-        <v>25262</v>
+        <v>25272</v>
       </c>
       <c r="H4" t="n">
         <v>5631</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2661452</v>
+        <v>2663370</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7448</v>
+        <v>7453</v>
       </c>
       <c r="O4" t="n">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P4" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="Q4" t="n">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="R4" t="n">
-        <v>14817</v>
+        <v>14827</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:09</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5160756</v>
+        <v>4.5166874</v>
       </c>
       <c r="G5" t="n">
-        <v>27144</v>
+        <v>27155</v>
       </c>
       <c r="H5" t="n">
-        <v>10104</v>
+        <v>10106</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>697911</v>
+        <v>698928</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2113</v>
+        <v>2102</v>
       </c>
       <c r="O5" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P5" t="n">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="Q5" t="n">
-        <v>1913</v>
+        <v>1890</v>
       </c>
       <c r="R5" t="n">
-        <v>21906</v>
+        <v>21929</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:09</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>114136</v>
+        <v>114259</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:09</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>463899</v>
+        <v>464326</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:10</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.201802</v>
+        <v>4.1913357</v>
       </c>
       <c r="G8" t="n">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="H8" t="n">
         <v>2308</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="R8" t="n">
-        <v>4652</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:10</t>
+          <t>2026-10-30 21:10:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>3.4322033</v>
       </c>
       <c r="G9" t="n">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H9" t="n">
         <v>566</v>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O9" t="n">
         <v>45</v>
@@ -1105,7 +1105,7 @@
         <v>34</v>
       </c>
       <c r="R9" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="10">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:10</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>99589</v>
+        <v>99914</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:10</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.651913</v>
+        <v>4.6501503</v>
       </c>
       <c r="G11" t="n">
-        <v>15038</v>
+        <v>15041</v>
       </c>
       <c r="H11" t="n">
         <v>709</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>315007</v>
+        <v>319559</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="O11" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P11" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="Q11" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="R11" t="n">
-        <v>12916</v>
+        <v>12906</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:11</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>363620</v>
+        <v>363945</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:11</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22668</v>
+        <v>22700</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:11</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.216783</v>
+        <v>4.2121916</v>
       </c>
       <c r="G14" t="n">
-        <v>14131</v>
+        <v>14140</v>
       </c>
       <c r="H14" t="n">
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1455,19 +1455,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2349</v>
+        <v>2366</v>
       </c>
       <c r="O14" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P14" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q14" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="R14" t="n">
-        <v>10935</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="15">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:11</t>
+          <t>2026-10-30 21:10:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3760684</v>
+        <v>3.3657143</v>
       </c>
       <c r="G15" t="n">
-        <v>3967</v>
+        <v>3970</v>
       </c>
       <c r="H15" t="n">
         <v>1603</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>425676</v>
+        <v>426436</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,19 +1529,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1411</v>
+        <v>1428</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="Q15" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R15" t="n">
-        <v>2146</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="16">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 21:29:11</t>
+          <t>2026-10-30 21:10:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.669114</v>
+        <v>4.668324</v>
       </c>
       <c r="G16" t="n">
-        <v>46838</v>
+        <v>46840</v>
       </c>
       <c r="H16" t="n">
-        <v>3053</v>
+        <v>3055</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>621904</v>
+        <v>624532</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1603,19 +1603,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2573</v>
+        <v>2583</v>
       </c>
       <c r="O16" t="n">
         <v>453</v>
       </c>
       <c r="P16" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="Q16" t="n">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="R16" t="n">
-        <v>40735</v>
+        <v>40729</v>
       </c>
     </row>
   </sheetData>
